--- a/data/data_spain.xlsx
+++ b/data/data_spain.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timotheedangleterre/Desktop/ENSAE/Semestre 1/ESSD/ProjetESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{EDADBD8D-CFB5-9649-8C91-E342319DCF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51787D77-3CCB-488F-A80C-BF1160514FD5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226F0863-A162-C345-AAAE-D928E329C871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2510" yWindow="1830" windowWidth="14400" windowHeight="7280" activeTab="1" xr2:uid="{92925F57-A0AC-404C-B2CD-8ED23E7BB18B}"/>
+    <workbookView xWindow="2520" yWindow="1840" windowWidth="23040" windowHeight="12260" xr2:uid="{92925F57-A0AC-404C-B2CD-8ED23E7BB18B}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenues" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,6 @@
     <author>tc={7C05136F-F1F6-1B48-A0FD-D9948482DAB4}</author>
     <author>tc={21B6A951-F9DD-EA4D-BBDB-1E84C1701EAC}</author>
     <author>tc={F2FC6E49-4445-9F42-A24F-41F47EAE24C1}</author>
-    <author>tc={0D899E68-CBC0-3C4E-A882-E37DCF27B76E}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{78C80B45-7F86-1D48-845D-369F96715558}">
@@ -122,14 +121,6 @@
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Yahoo finance log returns</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="8" shapeId="0" xr:uid="{0D899E68-CBC0-3C4E-A882-E37DCF27B76E}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    DBnomics</t>
       </text>
     </comment>
   </commentList>
@@ -260,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
   <si>
     <t>Dates</t>
   </si>
@@ -305,9 +296,6 @@
   </si>
   <si>
     <t xml:space="preserve">Stock market </t>
-  </si>
-  <si>
-    <t>Consumer confidence</t>
   </si>
   <si>
     <t>Total expenditure</t>
@@ -974,9 +962,6 @@
   <threadedComment ref="O1" dT="2026-02-09T16:46:20.14" personId="{E0F60C48-9375-0B4A-8578-0334C1C9071A}" id="{F2FC6E49-4445-9F42-A24F-41F47EAE24C1}">
     <text>Yahoo finance log returns</text>
   </threadedComment>
-  <threadedComment ref="P1" dT="2026-02-09T16:16:35.84" personId="{E0F60C48-9375-0B4A-8578-0334C1C9071A}" id="{0D899E68-CBC0-3C4E-A882-E37DCF27B76E}">
-    <text>DBnomics</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -1069,10 +1054,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC83A82-CE31-B84F-BDF7-6A55FA66BF4B}">
-  <dimension ref="A1:Q313"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:O313"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1118,11 +1103,8 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>36526</v>
       </c>
@@ -1156,15 +1138,8 @@
       <c r="O2">
         <v>0.149778350544578</v>
       </c>
-      <c r="P2">
-        <v>13.1</v>
-      </c>
-      <c r="Q2" t="str">
-        <f>IF(MONTH($A2) = 1, YEAR($A2)&amp;"-Q"&amp;MONTH($A2), IF(MONTH($A2) = 4, YEAR($A2)&amp;"-Q2", IF(MONTH($A2) = 7, YEAR($A2)&amp;"-Q3", IF(MONTH($A2) = 10, YEAR($A2)&amp;"-Q4",""))))</f>
-        <v>2000-Q1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>36557</v>
       </c>
@@ -1198,15 +1173,8 @@
       <c r="O3">
         <v>-5.3093918997033598E-2</v>
       </c>
-      <c r="P3">
-        <v>14.3</v>
-      </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q66" si="0">IF(MONTH($A3) = 1, YEAR($A3)&amp;"-Q"&amp;MONTH($A3), IF(MONTH($A3) = 4, YEAR($A3)&amp;"-Q2", IF(MONTH($A3) = 7, YEAR($A3)&amp;"-Q3", IF(MONTH($A3) = 10, YEAR($A3)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>36586</v>
       </c>
@@ -1240,15 +1208,8 @@
       <c r="O4">
         <v>-3.9923397661509E-2</v>
       </c>
-      <c r="P4">
-        <v>14.9</v>
-      </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>36617</v>
       </c>
@@ -1282,15 +1243,8 @@
       <c r="O5">
         <v>-7.03834649920871E-2</v>
       </c>
-      <c r="P5">
-        <v>13.8</v>
-      </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>36647</v>
       </c>
@@ -1324,15 +1278,8 @@
       <c r="O6">
         <v>-1.00801233676915E-2</v>
       </c>
-      <c r="P6">
-        <v>12.1</v>
-      </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>36678</v>
       </c>
@@ -1366,15 +1313,8 @@
       <c r="O7">
         <v>-4.7080494385127701E-3</v>
       </c>
-      <c r="P7">
-        <v>12.1</v>
-      </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>36708</v>
       </c>
@@ -1408,15 +1348,8 @@
       <c r="O8">
         <v>3.2977927055901197E-2</v>
       </c>
-      <c r="P8">
-        <v>12.4</v>
-      </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>36739</v>
       </c>
@@ -1450,15 +1383,8 @@
       <c r="O9">
         <v>5.9813048756147697E-3</v>
       </c>
-      <c r="P9">
-        <v>12.4</v>
-      </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>36770</v>
       </c>
@@ -1492,15 +1418,8 @@
       <c r="O10">
         <v>-5.5088074085491101E-2</v>
       </c>
-      <c r="P10">
-        <v>9.4</v>
-      </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>36800</v>
       </c>
@@ -1534,15 +1453,8 @@
       <c r="O11">
         <v>-0.117473051887064</v>
       </c>
-      <c r="P11">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>36831</v>
       </c>
@@ -1576,15 +1488,8 @@
       <c r="O12">
         <v>-1.1427594595717801E-2</v>
       </c>
-      <c r="P12">
-        <v>10.5</v>
-      </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>36861</v>
       </c>
@@ -1618,15 +1523,8 @@
       <c r="O13">
         <v>0.10476759311348301</v>
       </c>
-      <c r="P13">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>36892</v>
       </c>
@@ -1660,15 +1558,8 @@
       <c r="O14">
         <v>-5.7430547303566101E-2</v>
       </c>
-      <c r="P14">
-        <v>10.9</v>
-      </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>36923</v>
       </c>
@@ -1702,15 +1593,8 @@
       <c r="O15">
         <v>-2.57813272266194E-2</v>
       </c>
-      <c r="P15">
-        <v>10.5</v>
-      </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>36951</v>
       </c>
@@ -1744,15 +1628,8 @@
       <c r="O16">
         <v>4.7488399915295097E-2</v>
       </c>
-      <c r="P16">
-        <v>11.2</v>
-      </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>36982</v>
       </c>
@@ -1786,15 +1663,8 @@
       <c r="O17">
         <v>-2.7029353532659801E-2</v>
       </c>
-      <c r="P17">
-        <v>8</v>
-      </c>
-      <c r="Q17" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>37012</v>
       </c>
@@ -1828,15 +1698,8 @@
       <c r="O18">
         <v>-6.7744096073440105E-2</v>
       </c>
-      <c r="P18">
-        <v>8.6</v>
-      </c>
-      <c r="Q18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>37043</v>
       </c>
@@ -1870,15 +1733,8 @@
       <c r="O19">
         <v>-4.5910954782916798E-2</v>
       </c>
-      <c r="P19">
-        <v>8</v>
-      </c>
-      <c r="Q19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>37073</v>
       </c>
@@ -1912,15 +1768,8 @@
       <c r="O20">
         <v>-1.8916039115323399E-2</v>
       </c>
-      <c r="P20">
-        <v>7</v>
-      </c>
-      <c r="Q20" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>37104</v>
       </c>
@@ -1954,15 +1803,8 @@
       <c r="O21">
         <v>-0.129004090961299</v>
       </c>
-      <c r="P21">
-        <v>8.6</v>
-      </c>
-      <c r="Q21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>37135</v>
       </c>
@@ -1996,15 +1838,8 @@
       <c r="O22">
         <v>6.1033077007788698E-2</v>
       </c>
-      <c r="P22">
-        <v>7.3</v>
-      </c>
-      <c r="Q22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>37165</v>
       </c>
@@ -2038,15 +1873,8 @@
       <c r="O23">
         <v>7.3197096692430505E-2</v>
       </c>
-      <c r="P23">
-        <v>9.1</v>
-      </c>
-      <c r="Q23" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>37196</v>
       </c>
@@ -2080,15 +1908,8 @@
       <c r="O24">
         <v>3.9254107957749102E-3</v>
       </c>
-      <c r="P24">
-        <v>7.6</v>
-      </c>
-      <c r="Q24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>37226</v>
       </c>
@@ -2125,15 +1946,8 @@
       <c r="O25">
         <v>-4.2224136716805902E-2</v>
       </c>
-      <c r="P25">
-        <v>7.3</v>
-      </c>
-      <c r="Q25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>37257</v>
       </c>
@@ -2170,15 +1984,8 @@
       <c r="O26">
         <v>1.05154340908591E-2</v>
       </c>
-      <c r="P26">
-        <v>5.9</v>
-      </c>
-      <c r="Q26" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>37288</v>
       </c>
@@ -2215,15 +2022,8 @@
       <c r="O27">
         <v>1.39396581269189E-2</v>
       </c>
-      <c r="P27">
-        <v>6.8</v>
-      </c>
-      <c r="Q27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>37316</v>
       </c>
@@ -2260,15 +2060,8 @@
       <c r="O28">
         <v>-1.1619212827985901E-2</v>
       </c>
-      <c r="P28">
-        <v>5.4</v>
-      </c>
-      <c r="Q28" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>37347</v>
       </c>
@@ -2305,15 +2098,8 @@
       <c r="O29">
         <v>-2.5398309209352401E-2</v>
       </c>
-      <c r="P29">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="Q29" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>37377</v>
       </c>
@@ -2350,15 +2136,8 @@
       <c r="O30">
         <v>-0.13975564072369001</v>
       </c>
-      <c r="P30">
-        <v>5.7</v>
-      </c>
-      <c r="Q30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>37408</v>
       </c>
@@ -2395,15 +2174,8 @@
       <c r="O31">
         <v>-0.10093427074078699</v>
       </c>
-      <c r="P31">
-        <v>3.9</v>
-      </c>
-      <c r="Q31" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>37438</v>
       </c>
@@ -2440,15 +2212,8 @@
       <c r="O32">
         <v>2.9391219366694098E-2</v>
       </c>
-      <c r="P32">
-        <v>2.8</v>
-      </c>
-      <c r="Q32" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>37469</v>
       </c>
@@ -2485,15 +2250,8 @@
       <c r="O33">
         <v>-0.16960844917675999</v>
       </c>
-      <c r="P33">
-        <v>1.8</v>
-      </c>
-      <c r="Q33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>37500</v>
       </c>
@@ -2530,15 +2288,8 @@
       <c r="O34">
         <v>0.12247480519569</v>
       </c>
-      <c r="P34">
-        <v>5</v>
-      </c>
-      <c r="Q34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>37530</v>
       </c>
@@ -2575,15 +2326,8 @@
       <c r="O35">
         <v>8.5228972704078004E-2</v>
       </c>
-      <c r="P35">
-        <v>3.7</v>
-      </c>
-      <c r="Q35" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>37561</v>
       </c>
@@ -2620,15 +2364,8 @@
       <c r="O36">
         <v>-0.102065355330303</v>
       </c>
-      <c r="P36">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="Q36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>37591</v>
       </c>
@@ -2665,15 +2402,8 @@
       <c r="O37">
         <v>-1.4885995939222201E-2</v>
       </c>
-      <c r="P37">
-        <v>-1.4</v>
-      </c>
-      <c r="Q37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37622</v>
       </c>
@@ -2710,15 +2440,8 @@
       <c r="O38">
         <v>8.6548249075359997E-3</v>
       </c>
-      <c r="P38">
-        <v>-0.8</v>
-      </c>
-      <c r="Q38" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>37653</v>
       </c>
@@ -2755,15 +2478,8 @@
       <c r="O39">
         <v>-2.1719638861924299E-2</v>
       </c>
-      <c r="P39">
-        <v>-0.1</v>
-      </c>
-      <c r="Q39" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>37681</v>
       </c>
@@ -2800,15 +2516,8 @@
       <c r="O40">
         <v>0.100245677057549</v>
       </c>
-      <c r="P40">
-        <v>-0.6</v>
-      </c>
-      <c r="Q40" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>37712</v>
       </c>
@@ -2845,15 +2554,8 @@
       <c r="O41">
         <v>2.9235287786999499E-3</v>
       </c>
-      <c r="P41">
-        <v>1.3</v>
-      </c>
-      <c r="Q41" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>37742</v>
       </c>
@@ -2890,15 +2592,8 @@
       <c r="O42">
         <v>5.2889929511881199E-2</v>
       </c>
-      <c r="P42">
-        <v>2.7</v>
-      </c>
-      <c r="Q42" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>37773</v>
       </c>
@@ -2935,15 +2630,8 @@
       <c r="O43">
         <v>2.8686898941995099E-2</v>
       </c>
-      <c r="P43">
-        <v>3.9</v>
-      </c>
-      <c r="Q43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>37803</v>
       </c>
@@ -2980,15 +2668,8 @@
       <c r="O44">
         <v>6.9991973273300099E-3</v>
       </c>
-      <c r="P44">
-        <v>2.8</v>
-      </c>
-      <c r="Q44" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>37834</v>
       </c>
@@ -3025,15 +2706,8 @@
       <c r="O45">
         <v>-5.9040330609271101E-2</v>
       </c>
-      <c r="P45">
-        <v>3.8</v>
-      </c>
-      <c r="Q45" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>37865</v>
       </c>
@@ -3070,15 +2744,8 @@
       <c r="O46">
         <v>6.1596395643723802E-2</v>
       </c>
-      <c r="P46">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="Q46" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>37895</v>
       </c>
@@ -3115,15 +2782,8 @@
       <c r="O47">
         <v>1.71051312733859E-2</v>
       </c>
-      <c r="P47">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q47" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>37926</v>
       </c>
@@ -3160,15 +2820,8 @@
       <c r="O48">
         <v>6.4693653275687907E-2</v>
       </c>
-      <c r="P48">
-        <v>3.8</v>
-      </c>
-      <c r="Q48" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>37956</v>
       </c>
@@ -3205,15 +2858,8 @@
       <c r="O49">
         <v>2.4600522622714401E-2</v>
       </c>
-      <c r="P49">
-        <v>3.7</v>
-      </c>
-      <c r="Q49" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>37987</v>
       </c>
@@ -3250,15 +2896,8 @@
       <c r="O50">
         <v>3.9500104869208699E-2</v>
       </c>
-      <c r="P50">
-        <v>2.8</v>
-      </c>
-      <c r="Q50" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>38018</v>
       </c>
@@ -3295,15 +2934,8 @@
       <c r="O51">
         <v>-2.8439019520877899E-2</v>
       </c>
-      <c r="P51">
-        <v>3.5</v>
-      </c>
-      <c r="Q51" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>38047</v>
       </c>
@@ -3340,15 +2972,8 @@
       <c r="O52">
         <v>1.1334715685451999E-2</v>
       </c>
-      <c r="P52">
-        <v>3.5</v>
-      </c>
-      <c r="Q52" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>38078</v>
       </c>
@@ -3385,15 +3010,8 @@
       <c r="O53">
         <v>-1.8695182193635401E-2</v>
       </c>
-      <c r="P53">
-        <v>4.7</v>
-      </c>
-      <c r="Q53" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>38108</v>
       </c>
@@ -3430,15 +3048,8 @@
       <c r="O54">
         <v>1.48403984276495E-2</v>
       </c>
-      <c r="P54">
-        <v>4.5</v>
-      </c>
-      <c r="Q54" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>38139</v>
       </c>
@@ -3475,15 +3086,8 @@
       <c r="O55">
         <v>-1.9878636760601899E-2</v>
       </c>
-      <c r="P55">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q55" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>38169</v>
       </c>
@@ -3520,15 +3124,8 @@
       <c r="O56">
         <v>-6.3082654095012501E-3</v>
       </c>
-      <c r="P56">
-        <v>3.3</v>
-      </c>
-      <c r="Q56" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>38200</v>
       </c>
@@ -3565,15 +3162,8 @@
       <c r="O57">
         <v>2.0090392910391899E-2</v>
       </c>
-      <c r="P57">
-        <v>1.9</v>
-      </c>
-      <c r="Q57" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>38231</v>
       </c>
@@ -3610,15 +3200,8 @@
       <c r="O58">
         <v>4.7322963511255998E-2</v>
       </c>
-      <c r="P58">
-        <v>1.9</v>
-      </c>
-      <c r="Q58" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>38261</v>
       </c>
@@ -3655,15 +3238,8 @@
       <c r="O59">
         <v>3.2110219665760602E-2</v>
       </c>
-      <c r="P59">
-        <v>3.8</v>
-      </c>
-      <c r="Q59" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>38292</v>
       </c>
@@ -3700,15 +3276,8 @@
       <c r="O60">
         <v>4.3644168853774097E-2</v>
       </c>
-      <c r="P60">
-        <v>3.3</v>
-      </c>
-      <c r="Q60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>38322</v>
       </c>
@@ -3745,15 +3314,8 @@
       <c r="O61">
         <v>1.5635711022904199E-2</v>
       </c>
-      <c r="P61">
-        <v>4</v>
-      </c>
-      <c r="Q61" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>38353</v>
       </c>
@@ -3790,15 +3352,8 @@
       <c r="O62">
         <v>1.7953799848871899E-2</v>
       </c>
-      <c r="P62">
-        <v>3</v>
-      </c>
-      <c r="Q62" t="str">
-        <f t="shared" si="0"/>
-        <v>2005-Q1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>38384</v>
       </c>
@@ -3835,15 +3390,8 @@
       <c r="O63">
         <v>-1.4177354289476101E-2</v>
       </c>
-      <c r="P63">
-        <v>2.9</v>
-      </c>
-      <c r="Q63" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>38412</v>
       </c>
@@ -3880,15 +3428,8 @@
       <c r="O64">
         <v>-2.8172133614663902E-2</v>
       </c>
-      <c r="P64">
-        <v>1.8</v>
-      </c>
-      <c r="Q64" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>38443</v>
       </c>
@@ -3925,15 +3466,8 @@
       <c r="O65">
         <v>4.6186182831599303E-2</v>
       </c>
-      <c r="P65">
-        <v>2.4</v>
-      </c>
-      <c r="Q65" t="str">
-        <f t="shared" si="0"/>
-        <v>2005-Q2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>38473</v>
       </c>
@@ -3970,15 +3504,8 @@
       <c r="O66">
         <v>3.7078170107157901E-2</v>
       </c>
-      <c r="P66">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>38504</v>
       </c>
@@ -4015,15 +3542,8 @@
       <c r="O67">
         <v>3.3412099232066297E-2</v>
       </c>
-      <c r="P67">
-        <v>2.4</v>
-      </c>
-      <c r="Q67" t="str">
-        <f t="shared" ref="Q67:Q130" si="1">IF(MONTH($A67) = 1, YEAR($A67)&amp;"-Q"&amp;MONTH($A67), IF(MONTH($A67) = 4, YEAR($A67)&amp;"-Q2", IF(MONTH($A67) = 7, YEAR($A67)&amp;"-Q3", IF(MONTH($A67) = 10, YEAR($A67)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>38534</v>
       </c>
@@ -4060,15 +3580,8 @@
       <c r="O68">
         <v>-1.0604011882517E-2</v>
       </c>
-      <c r="P68">
-        <v>2.5</v>
-      </c>
-      <c r="Q68" t="str">
-        <f t="shared" si="1"/>
-        <v>2005-Q3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>38565</v>
       </c>
@@ -4105,15 +3618,8 @@
       <c r="O69">
         <v>7.7357643560848302E-2</v>
       </c>
-      <c r="P69">
-        <v>2.7</v>
-      </c>
-      <c r="Q69" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>38596</v>
       </c>
@@ -4150,15 +3656,8 @@
       <c r="O70">
         <v>-3.0047791806392599E-2</v>
       </c>
-      <c r="P70">
-        <v>2.4</v>
-      </c>
-      <c r="Q70" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>38626</v>
       </c>
@@ -4195,15 +3694,8 @@
       <c r="O71">
         <v>6.0803167799239298E-3</v>
       </c>
-      <c r="P71">
-        <v>2.7</v>
-      </c>
-      <c r="Q71" t="str">
-        <f t="shared" si="1"/>
-        <v>2005-Q4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>38657</v>
       </c>
@@ -4240,15 +3732,8 @@
       <c r="O72">
         <v>1.6542089170389601E-2</v>
       </c>
-      <c r="P72">
-        <v>-0.3</v>
-      </c>
-      <c r="Q72" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>38687</v>
       </c>
@@ -4285,15 +3770,8 @@
       <c r="O73">
         <v>3.3925409190235498E-2</v>
       </c>
-      <c r="P73">
-        <v>2.4</v>
-      </c>
-      <c r="Q73" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>38718</v>
       </c>
@@ -4330,15 +3808,8 @@
       <c r="O74">
         <v>5.5729051369244297E-2</v>
       </c>
-      <c r="P74">
-        <v>0.1</v>
-      </c>
-      <c r="Q74" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>38749</v>
       </c>
@@ -4375,15 +3846,8 @@
       <c r="O75">
         <v>9.6292000113660202E-3</v>
       </c>
-      <c r="P75">
-        <v>-0.1</v>
-      </c>
-      <c r="Q75" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>38777</v>
       </c>
@@ -4420,15 +3884,8 @@
       <c r="O76">
         <v>3.2172948420417001E-3</v>
       </c>
-      <c r="P76">
-        <v>-0.1</v>
-      </c>
-      <c r="Q76" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>38808</v>
       </c>
@@ -4465,15 +3922,8 @@
       <c r="O77">
         <v>-4.7527560285946201E-2</v>
       </c>
-      <c r="P77">
-        <v>0.9</v>
-      </c>
-      <c r="Q77" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>38838</v>
       </c>
@@ -4510,15 +3960,8 @@
       <c r="O78">
         <v>1.8140498407069199E-2</v>
       </c>
-      <c r="P78">
-        <v>-0.3</v>
-      </c>
-      <c r="Q78" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>38869</v>
       </c>
@@ -4555,15 +3998,8 @@
       <c r="O79">
         <v>2.31029054780603E-2</v>
       </c>
-      <c r="P79">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="Q79" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>38899</v>
       </c>
@@ -4600,15 +4036,8 @@
       <c r="O80">
         <v>2.72690837844216E-2</v>
       </c>
-      <c r="P80">
-        <v>-0.6</v>
-      </c>
-      <c r="Q80" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>38930</v>
       </c>
@@ -4645,15 +4074,8 @@
       <c r="O81">
         <v>6.3020760873499199E-2</v>
       </c>
-      <c r="P81">
-        <v>0.8</v>
-      </c>
-      <c r="Q81" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>38961</v>
       </c>
@@ -4690,15 +4112,8 @@
       <c r="O82">
         <v>6.1343344551167099E-2</v>
       </c>
-      <c r="P82">
-        <v>-0.1</v>
-      </c>
-      <c r="Q82" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>38991</v>
       </c>
@@ -4735,15 +4150,8 @@
       <c r="O83">
         <v>6.9776936045666798E-3</v>
       </c>
-      <c r="P83">
-        <v>2.7</v>
-      </c>
-      <c r="Q83" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>39022</v>
       </c>
@@ -4780,15 +4188,8 @@
       <c r="O84">
         <v>2.1232567932774098E-2</v>
       </c>
-      <c r="P84">
-        <v>3.2</v>
-      </c>
-      <c r="Q84" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>39052</v>
       </c>
@@ -4825,15 +4226,8 @@
       <c r="O85">
         <v>2.8343670458317798E-2</v>
       </c>
-      <c r="P85">
-        <v>2.1</v>
-      </c>
-      <c r="Q85" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>39083</v>
       </c>
@@ -4870,15 +4264,8 @@
       <c r="O86">
         <v>-2.11662670039168E-2</v>
       </c>
-      <c r="P86">
-        <v>0.1</v>
-      </c>
-      <c r="Q86" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>39114</v>
       </c>
@@ -4915,15 +4302,8 @@
       <c r="O87">
         <v>2.7228988225470398E-2</v>
       </c>
-      <c r="P87">
-        <v>0.6</v>
-      </c>
-      <c r="Q87" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>39142</v>
       </c>
@@ -4960,15 +4340,8 @@
       <c r="O88">
         <v>-1.8410902315148199E-2</v>
       </c>
-      <c r="P88">
-        <v>1.3</v>
-      </c>
-      <c r="Q88" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>39173</v>
       </c>
@@ -5005,15 +4378,8 @@
       <c r="O89">
         <v>6.4309845621970396E-2</v>
       </c>
-      <c r="P89">
-        <v>0.2</v>
-      </c>
-      <c r="Q89" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>39203</v>
       </c>
@@ -5050,15 +4416,8 @@
       <c r="O90">
         <v>-2.8948422646134699E-2</v>
       </c>
-      <c r="P90">
-        <v>0.1</v>
-      </c>
-      <c r="Q90" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>39234</v>
       </c>
@@ -5095,15 +4454,8 @@
       <c r="O91">
         <v>-6.0347998358007996E-3</v>
       </c>
-      <c r="P91">
-        <v>0.6</v>
-      </c>
-      <c r="Q91" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>39264</v>
       </c>
@@ -5140,15 +4492,8 @@
       <c r="O92">
         <v>-2.2034794955803998E-2</v>
       </c>
-      <c r="P92">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q92" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>39295</v>
       </c>
@@ -5185,15 +4530,8 @@
       <c r="O93">
         <v>6.6560816741798598E-3</v>
       </c>
-      <c r="P93">
-        <v>0.1</v>
-      </c>
-      <c r="Q93" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>39326</v>
       </c>
@@ -5230,15 +4568,8 @@
       <c r="O94">
         <v>8.6310803491549806E-2</v>
       </c>
-      <c r="P94">
-        <v>-1.7</v>
-      </c>
-      <c r="Q94" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>39356</v>
       </c>
@@ -5275,15 +4606,8 @@
       <c r="O95">
         <v>-8.2526823666508892E-3</v>
       </c>
-      <c r="P95">
-        <v>-2.5</v>
-      </c>
-      <c r="Q95" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>39387</v>
       </c>
@@ -5320,15 +4644,8 @@
       <c r="O96">
         <v>-3.7338501240693503E-2</v>
       </c>
-      <c r="P96">
-        <v>-4.4000000000000004</v>
-      </c>
-      <c r="Q96" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>39417</v>
       </c>
@@ -5365,15 +4682,8 @@
       <c r="O97">
         <v>-0.13771887329700799</v>
       </c>
-      <c r="P97">
-        <v>-7.8</v>
-      </c>
-      <c r="Q97" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>39448</v>
       </c>
@@ -5410,15 +4720,8 @@
       <c r="O98">
         <v>-4.4394724692580203E-3</v>
       </c>
-      <c r="P98">
-        <v>-8.4</v>
-      </c>
-      <c r="Q98" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>39479</v>
       </c>
@@ -5455,15 +4758,8 @@
       <c r="O99">
         <v>7.4585705433136704E-3</v>
       </c>
-      <c r="P99">
-        <v>-8.9</v>
-      </c>
-      <c r="Q99" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>39508</v>
       </c>
@@ -5500,15 +4796,8 @@
       <c r="O100">
         <v>3.9114894459924401E-2</v>
       </c>
-      <c r="P100">
-        <v>-8.1</v>
-      </c>
-      <c r="Q100" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>39539</v>
       </c>
@@ -5545,15 +4834,8 @@
       <c r="O101">
         <v>-1.4409386270669299E-2</v>
       </c>
-      <c r="P101">
-        <v>-11.7</v>
-      </c>
-      <c r="Q101" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>39569</v>
       </c>
@@ -5590,15 +4872,8 @@
       <c r="O102">
         <v>-0.121386722024484</v>
       </c>
-      <c r="P102">
-        <v>-15.8</v>
-      </c>
-      <c r="Q102" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>39600</v>
       </c>
@@ -5635,15 +4910,8 @@
       <c r="O103">
         <v>-1.3783554600555799E-2</v>
       </c>
-      <c r="P103">
-        <v>-22.3</v>
-      </c>
-      <c r="Q103" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>39630</v>
       </c>
@@ -5680,15 +4948,8 @@
       <c r="O104">
         <v>-1.47531569382497E-2</v>
       </c>
-      <c r="P104">
-        <v>-23.3</v>
-      </c>
-      <c r="Q104" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>39661</v>
       </c>
@@ -5725,15 +4986,8 @@
       <c r="O105">
         <v>-6.3454299168968803E-2</v>
       </c>
-      <c r="P105">
-        <v>-20</v>
-      </c>
-      <c r="Q105" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>39692</v>
       </c>
@@ -5770,15 +5024,8 @@
       <c r="O106">
         <v>-0.186727151627858</v>
       </c>
-      <c r="P106">
-        <v>-20.8</v>
-      </c>
-      <c r="Q106" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>39722</v>
       </c>
@@ -5815,15 +5062,8 @@
       <c r="O107">
         <v>-2.2789575938858799E-2</v>
       </c>
-      <c r="P107">
-        <v>-24.3</v>
-      </c>
-      <c r="Q107" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>39753</v>
       </c>
@@ -5860,15 +5100,8 @@
       <c r="O108">
         <v>3.1505301394194198E-2</v>
       </c>
-      <c r="P108">
-        <v>-23.2</v>
-      </c>
-      <c r="Q108" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>39783</v>
       </c>
@@ -5905,15 +5138,8 @@
       <c r="O109">
         <v>-8.4533013086335998E-2</v>
       </c>
-      <c r="P109">
-        <v>-24</v>
-      </c>
-      <c r="Q109" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>39814</v>
       </c>
@@ -5950,15 +5176,8 @@
       <c r="O110">
         <v>-0.103319363606394</v>
       </c>
-      <c r="P110">
-        <v>-23.5</v>
-      </c>
-      <c r="Q110" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>39845</v>
       </c>
@@ -5995,15 +5214,8 @@
       <c r="O111">
         <v>2.5150503727395801E-2</v>
       </c>
-      <c r="P111">
-        <v>-27.9</v>
-      </c>
-      <c r="Q111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>39873</v>
       </c>
@@ -6040,15 +5252,8 @@
       <c r="O112">
         <v>0.14539294711564901</v>
       </c>
-      <c r="P112">
-        <v>-21.5</v>
-      </c>
-      <c r="Q112" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>39904</v>
       </c>
@@ -6085,15 +5290,8 @@
       <c r="O113">
         <v>4.18535283054116E-2</v>
       </c>
-      <c r="P113">
-        <v>-18.5</v>
-      </c>
-      <c r="Q113" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>39934</v>
       </c>
@@ -6130,15 +5328,8 @@
       <c r="O114">
         <v>3.78452529389861E-2</v>
       </c>
-      <c r="P114">
-        <v>-13.6</v>
-      </c>
-      <c r="Q114" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>39965</v>
       </c>
@@ -6175,15 +5366,8 @@
       <c r="O115">
         <v>0.103498287413487</v>
       </c>
-      <c r="P115">
-        <v>-12.7</v>
-      </c>
-      <c r="Q115" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>39995</v>
       </c>
@@ -6220,15 +5404,8 @@
       <c r="O116">
         <v>4.5912242192375899E-2</v>
       </c>
-      <c r="P116">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="Q116" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>40026</v>
       </c>
@@ -6265,15 +5442,8 @@
       <c r="O117">
         <v>3.3824999748370402E-2</v>
       </c>
-      <c r="P117">
-        <v>-8.8000000000000007</v>
-      </c>
-      <c r="Q117" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>40057</v>
       </c>
@@ -6310,15 +5480,8 @@
       <c r="O118">
         <v>-2.9461479675870102E-2</v>
       </c>
-      <c r="P118">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="Q118" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>40087</v>
       </c>
@@ -6355,15 +5518,8 @@
       <c r="O119">
         <v>1.9940415735588201E-2</v>
       </c>
-      <c r="P119">
-        <v>-9.1</v>
-      </c>
-      <c r="Q119" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>40118</v>
       </c>
@@ -6400,15 +5556,8 @@
       <c r="O120">
         <v>2.5042950317018899E-2</v>
       </c>
-      <c r="P120">
-        <v>-9.6</v>
-      </c>
-      <c r="Q120" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>40148</v>
       </c>
@@ -6445,15 +5594,8 @@
       <c r="O121">
         <v>-8.6764701586220697E-2</v>
       </c>
-      <c r="P121">
-        <v>-7</v>
-      </c>
-      <c r="Q121" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>40179</v>
       </c>
@@ -6490,15 +5632,8 @@
       <c r="O122">
         <v>-5.77287222440113E-2</v>
       </c>
-      <c r="P122">
-        <v>-7</v>
-      </c>
-      <c r="Q122" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>40210</v>
       </c>
@@ -6535,15 +5670,8 @@
       <c r="O123">
         <v>5.0725587098265003E-2</v>
       </c>
-      <c r="P123">
-        <v>-9.8000000000000007</v>
-      </c>
-      <c r="Q123" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>40238</v>
       </c>
@@ -6580,15 +5708,8 @@
       <c r="O124">
         <v>-3.5494128651938801E-2</v>
       </c>
-      <c r="P124">
-        <v>-10.9</v>
-      </c>
-      <c r="Q124" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>40269</v>
       </c>
@@ -6625,15 +5746,8 @@
       <c r="O125">
         <v>-0.11425091497369499</v>
       </c>
-      <c r="P125">
-        <v>-10.199999999999999</v>
-      </c>
-      <c r="Q125" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>40299</v>
       </c>
@@ -6670,15 +5784,8 @@
       <c r="O126">
         <v>-1.03100335444157E-2</v>
       </c>
-      <c r="P126">
-        <v>-13.7</v>
-      </c>
-      <c r="Q126" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>40330</v>
       </c>
@@ -6715,15 +5822,8 @@
       <c r="O127">
         <v>0.125284996699037</v>
       </c>
-      <c r="P127">
-        <v>-16.8</v>
-      </c>
-      <c r="Q127" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>40360</v>
       </c>
@@ -6760,15 +5860,8 @@
       <c r="O128">
         <v>-3.0243793153546899E-2</v>
       </c>
-      <c r="P128">
-        <v>-16.2</v>
-      </c>
-      <c r="Q128" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>40391</v>
       </c>
@@ -6805,15 +5898,8 @@
       <c r="O129">
         <v>3.16428592986924E-2</v>
       </c>
-      <c r="P129">
-        <v>-11.3</v>
-      </c>
-      <c r="Q129" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>40422</v>
       </c>
@@ -6850,15 +5936,8 @@
       <c r="O130">
         <v>2.79846450125909E-2</v>
       </c>
-      <c r="P130">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="Q130" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>40452</v>
       </c>
@@ -6895,15 +5974,8 @@
       <c r="O131">
         <v>-0.154258596514387</v>
       </c>
-      <c r="P131">
-        <v>-10.5</v>
-      </c>
-      <c r="Q131" t="str">
-        <f t="shared" ref="Q131:Q194" si="2">IF(MONTH($A131) = 1, YEAR($A131)&amp;"-Q"&amp;MONTH($A131), IF(MONTH($A131) = 4, YEAR($A131)&amp;"-Q2", IF(MONTH($A131) = 7, YEAR($A131)&amp;"-Q3", IF(MONTH($A131) = 10, YEAR($A131)&amp;"-Q4",""))))</f>
-        <v>2010-Q4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>40483</v>
       </c>
@@ -6940,15 +6012,8 @@
       <c r="O132">
         <v>6.1913541532414101E-2</v>
       </c>
-      <c r="P132">
-        <v>-11.1</v>
-      </c>
-      <c r="Q132" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>40513</v>
       </c>
@@ -6985,15 +6050,8 @@
       <c r="O133">
         <v>9.1706688484633106E-2</v>
       </c>
-      <c r="P133">
-        <v>-13.2</v>
-      </c>
-      <c r="Q133" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>40544</v>
       </c>
@@ -7030,15 +6088,8 @@
       <c r="O134">
         <v>4.1372565655404302E-3</v>
       </c>
-      <c r="P134">
-        <v>-13.8</v>
-      </c>
-      <c r="Q134" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>40575</v>
       </c>
@@ -7075,15 +6126,8 @@
       <c r="O135">
         <v>-2.5604233142345799E-2</v>
       </c>
-      <c r="P135">
-        <v>-11.4</v>
-      </c>
-      <c r="Q135" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>40603</v>
       </c>
@@ -7120,15 +6164,8 @@
       <c r="O136">
         <v>2.8190610436967099E-2</v>
       </c>
-      <c r="P136">
-        <v>-11.4</v>
-      </c>
-      <c r="Q136" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>40634</v>
       </c>
@@ -7165,15 +6202,8 @@
       <c r="O137">
         <v>-3.7738242636569601E-2</v>
       </c>
-      <c r="P137">
-        <v>-12.2</v>
-      </c>
-      <c r="Q137" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>40664</v>
       </c>
@@ -7210,15 +6240,8 @@
       <c r="O138">
         <v>-1.11443046648887E-2</v>
       </c>
-      <c r="P138">
-        <v>-9.9</v>
-      </c>
-      <c r="Q138" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>40695</v>
       </c>
@@ -7255,15 +6278,8 @@
       <c r="O139">
         <v>-7.2986689020158493E-2</v>
       </c>
-      <c r="P139">
-        <v>-9.6</v>
-      </c>
-      <c r="Q139" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>40725</v>
       </c>
@@ -7300,15 +6316,8 @@
       <c r="O140">
         <v>-9.9497303191489195E-2</v>
       </c>
-      <c r="P140">
-        <v>-8.6</v>
-      </c>
-      <c r="Q140" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>40756</v>
       </c>
@@ -7345,15 +6354,8 @@
       <c r="O141">
         <v>-1.99251324323164E-2</v>
       </c>
-      <c r="P141">
-        <v>-10.9</v>
-      </c>
-      <c r="Q141" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>40787</v>
       </c>
@@ -7390,15 +6392,8 @@
       <c r="O142">
         <v>4.66674147892387E-2</v>
       </c>
-      <c r="P142">
-        <v>-11.1</v>
-      </c>
-      <c r="Q142" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>40817</v>
       </c>
@@ -7435,15 +6430,8 @@
       <c r="O143">
         <v>-5.8093644105110101E-2</v>
       </c>
-      <c r="P143">
-        <v>-13.1</v>
-      </c>
-      <c r="Q143" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>40848</v>
       </c>
@@ -7480,15 +6468,8 @@
       <c r="O144">
         <v>1.37286099397897E-2</v>
       </c>
-      <c r="P144">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="Q144" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>40878</v>
       </c>
@@ -7525,15 +6506,8 @@
       <c r="O145">
         <v>-6.6879238916186497E-3</v>
       </c>
-      <c r="P145">
-        <v>-9.8000000000000007</v>
-      </c>
-      <c r="Q145" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>40909</v>
       </c>
@@ -7570,15 +6544,8 @@
       <c r="O146">
         <v>-5.10157785265086E-3</v>
       </c>
-      <c r="P146">
-        <v>-14.7</v>
-      </c>
-      <c r="Q146" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>40940</v>
       </c>
@@ -7615,15 +6582,8 @@
       <c r="O147">
         <v>-5.5605334203342197E-2</v>
       </c>
-      <c r="P147">
-        <v>-15.9</v>
-      </c>
-      <c r="Q147" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>40969</v>
       </c>
@@ -7660,15 +6620,8 @@
       <c r="O148">
         <v>-0.132960697788089</v>
       </c>
-      <c r="P148">
-        <v>-18.399999999999999</v>
-      </c>
-      <c r="Q148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>41000</v>
       </c>
@@ -7705,15 +6658,8 @@
       <c r="O149">
         <v>-0.140865135836862</v>
       </c>
-      <c r="P149">
-        <v>-20</v>
-      </c>
-      <c r="Q149" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>41030</v>
       </c>
@@ -7750,15 +6696,8 @@
       <c r="O150">
         <v>0.15378941431807799</v>
       </c>
-      <c r="P150">
-        <v>-22.1</v>
-      </c>
-      <c r="Q150" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>41061</v>
       </c>
@@ -7795,15 +6734,8 @@
       <c r="O151">
         <v>-5.2626622139502602E-2</v>
       </c>
-      <c r="P151">
-        <v>-19.2</v>
-      </c>
-      <c r="Q151" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>41091</v>
       </c>
@@ -7840,15 +6772,8 @@
       <c r="O152">
         <v>9.6468439787191301E-2</v>
       </c>
-      <c r="P152">
-        <v>-21.6</v>
-      </c>
-      <c r="Q152" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>41122</v>
       </c>
@@ -7885,15 +6810,8 @@
       <c r="O153">
         <v>3.8077175764520597E-2</v>
       </c>
-      <c r="P153">
-        <v>-28.1</v>
-      </c>
-      <c r="Q153" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>41153</v>
       </c>
@@ -7930,15 +6848,8 @@
       <c r="O154">
         <v>1.7285035356310999E-2</v>
       </c>
-      <c r="P154">
-        <v>-25.2</v>
-      </c>
-      <c r="Q154" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>41183</v>
       </c>
@@ -7975,15 +6886,8 @@
       <c r="O155">
         <v>1.16243039630266E-2</v>
       </c>
-      <c r="P155">
-        <v>-22.7</v>
-      </c>
-      <c r="Q155" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>41214</v>
       </c>
@@ -8020,15 +6924,8 @@
       <c r="O156">
         <v>2.8929909055493801E-2</v>
       </c>
-      <c r="P156">
-        <v>-22.9</v>
-      </c>
-      <c r="Q156" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>41244</v>
       </c>
@@ -8065,15 +6962,8 @@
       <c r="O157">
         <v>2.3570621025971399E-2</v>
       </c>
-      <c r="P157">
-        <v>-24.7</v>
-      </c>
-      <c r="Q157" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>41275</v>
       </c>
@@ -8110,15 +7000,8 @@
       <c r="O158">
         <v>-1.59110432204876E-2</v>
       </c>
-      <c r="P158">
-        <v>-20.3</v>
-      </c>
-      <c r="Q158" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>41306</v>
       </c>
@@ -8155,15 +7038,8 @@
       <c r="O159">
         <v>-3.8431236472236598E-2</v>
       </c>
-      <c r="P159">
-        <v>-21.4</v>
-      </c>
-      <c r="Q159" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>41334</v>
       </c>
@@ -8200,15 +7076,8 @@
       <c r="O160">
         <v>6.1099850529192402E-2</v>
       </c>
-      <c r="P160">
-        <v>-19</v>
-      </c>
-      <c r="Q160" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>41365</v>
       </c>
@@ -8245,15 +7114,8 @@
       <c r="O161">
         <v>-1.1756735684720399E-2</v>
       </c>
-      <c r="P161">
-        <v>-18.7</v>
-      </c>
-      <c r="Q161" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>41395</v>
       </c>
@@ -8290,15 +7152,8 @@
       <c r="O162">
         <v>-6.9404083687407706E-2</v>
       </c>
-      <c r="P162">
-        <v>-19.899999999999999</v>
-      </c>
-      <c r="Q162" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>41426</v>
       </c>
@@ -8335,15 +7190,8 @@
       <c r="O163">
         <v>8.2869821507863206E-2</v>
       </c>
-      <c r="P163">
-        <v>-17.3</v>
-      </c>
-      <c r="Q163" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>41456</v>
       </c>
@@ -8380,15 +7228,8 @@
       <c r="O164">
         <v>-1.7089777531971599E-2</v>
       </c>
-      <c r="P164">
-        <v>-12.9</v>
-      </c>
-      <c r="Q164" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>41487</v>
       </c>
@@ -8425,15 +7266,8 @@
       <c r="O165">
         <v>0.102581148492639</v>
       </c>
-      <c r="P165">
-        <v>-11.9</v>
-      </c>
-      <c r="Q165" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>41518</v>
       </c>
@@ -8470,15 +7304,8 @@
       <c r="O166">
         <v>7.5641028695599702E-2</v>
       </c>
-      <c r="P166">
-        <v>-7.7</v>
-      </c>
-      <c r="Q166" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>41548</v>
       </c>
@@ -8515,15 +7342,8 @@
       <c r="O167">
         <v>-7.1207189787774201E-3</v>
       </c>
-      <c r="P167">
-        <v>-10.5</v>
-      </c>
-      <c r="Q167" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q4</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>41579</v>
       </c>
@@ -8560,15 +7380,8 @@
       <c r="O168">
         <v>8.0084851889772306E-3</v>
       </c>
-      <c r="P168">
-        <v>-9.1999999999999993</v>
-      </c>
-      <c r="Q168" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>41609</v>
       </c>
@@ -8605,15 +7418,8 @@
       <c r="O169">
         <v>3.5287771450143201E-4</v>
       </c>
-      <c r="P169">
-        <v>-9</v>
-      </c>
-      <c r="Q169" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>41640</v>
       </c>
@@ -8650,15 +7456,8 @@
       <c r="O170">
         <v>1.9367294270670899E-2</v>
       </c>
-      <c r="P170">
-        <v>-6.6</v>
-      </c>
-      <c r="Q170" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>41671</v>
       </c>
@@ -8695,15 +7494,8 @@
       <c r="O171">
         <v>2.2127827467691898E-2</v>
       </c>
-      <c r="P171">
-        <v>-7.5</v>
-      </c>
-      <c r="Q171" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>41699</v>
       </c>
@@ -8740,15 +7532,8 @@
       <c r="O172">
         <v>1.1394627961537999E-2</v>
       </c>
-      <c r="P172">
-        <v>-4.5</v>
-      </c>
-      <c r="Q172" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>41730</v>
       </c>
@@ -8785,15 +7570,8 @@
       <c r="O173">
         <v>3.1962922829244199E-2</v>
       </c>
-      <c r="P173">
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="Q173" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>41760</v>
       </c>
@@ -8830,15 +7608,8 @@
       <c r="O174">
         <v>1.1490657182633901E-2</v>
       </c>
-      <c r="P174">
-        <v>-4.3</v>
-      </c>
-      <c r="Q174" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>41791</v>
       </c>
@@ -8875,15 +7646,8 @@
       <c r="O175">
         <v>-2.00000011724661E-2</v>
       </c>
-      <c r="P175">
-        <v>-1.3</v>
-      </c>
-      <c r="Q175" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>41821</v>
       </c>
@@ -8920,15 +7684,8 @@
       <c r="O176">
         <v>2.01526559854415E-3</v>
       </c>
-      <c r="P176">
-        <v>-2.5</v>
-      </c>
-      <c r="Q176" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>41852</v>
       </c>
@@ -8965,15 +7722,8 @@
       <c r="O177">
         <v>8.9727659882132792E-3</v>
       </c>
-      <c r="P177">
-        <v>-0.6</v>
-      </c>
-      <c r="Q177" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>41883</v>
       </c>
@@ -9010,15 +7760,8 @@
       <c r="O178">
         <v>-3.2645747647185502E-2</v>
       </c>
-      <c r="P178">
-        <v>-0.8</v>
-      </c>
-      <c r="Q178" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>41913</v>
       </c>
@@ -9055,15 +7798,8 @@
       <c r="O179">
         <v>2.75707879962361E-2</v>
       </c>
-      <c r="P179">
-        <v>-1.3</v>
-      </c>
-      <c r="Q179" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>41944</v>
       </c>
@@ -9100,15 +7836,8 @@
       <c r="O180">
         <v>-4.6677881835501402E-2</v>
       </c>
-      <c r="P180">
-        <v>-3.3</v>
-      </c>
-      <c r="Q180" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>41974</v>
       </c>
@@ -9145,15 +7874,8 @@
       <c r="O181">
         <v>1.1971424022254601E-2</v>
       </c>
-      <c r="P181">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>42005</v>
       </c>
@@ -9190,15 +7912,8 @@
       <c r="O182">
         <v>7.1851336713423905E-2</v>
       </c>
-      <c r="P182">
-        <v>4.8</v>
-      </c>
-      <c r="Q182" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>42036</v>
       </c>
@@ -9235,15 +7950,8 @@
       <c r="O183">
         <v>3.0205721467636299E-2</v>
       </c>
-      <c r="P183">
-        <v>4.7</v>
-      </c>
-      <c r="Q183" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>42064</v>
       </c>
@@ -9280,15 +7988,8 @@
       <c r="O184">
         <v>-1.18834033994624E-2</v>
       </c>
-      <c r="P184">
-        <v>7.3</v>
-      </c>
-      <c r="Q184" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>42095</v>
       </c>
@@ -9325,15 +8026,8 @@
       <c r="O185">
         <v>-1.48127608676489E-2</v>
       </c>
-      <c r="P185">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="Q185" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>42125</v>
       </c>
@@ -9370,15 +8064,8 @@
       <c r="O186">
         <v>-4.0765873812780698E-2</v>
       </c>
-      <c r="P186">
-        <v>6.6</v>
-      </c>
-      <c r="Q186" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>42156</v>
       </c>
@@ -9415,15 +8102,8 @@
       <c r="O187">
         <v>3.74710302071595E-2</v>
       </c>
-      <c r="P187">
-        <v>5.7</v>
-      </c>
-      <c r="Q187" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>42186</v>
       </c>
@@ -9460,15 +8140,8 @@
       <c r="O188">
         <v>-8.6033725936857805E-2</v>
       </c>
-      <c r="P188">
-        <v>5.9</v>
-      </c>
-      <c r="Q188" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>42217</v>
       </c>
@@ -9505,15 +8178,8 @@
       <c r="O189">
         <v>-7.0578061487237803E-2</v>
       </c>
-      <c r="P189">
-        <v>6.7</v>
-      </c>
-      <c r="Q189" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>42248</v>
       </c>
@@ -9550,15 +8216,8 @@
       <c r="O190">
         <v>8.0442513349266803E-2</v>
       </c>
-      <c r="P190">
-        <v>7.8</v>
-      </c>
-      <c r="Q190" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>42278</v>
       </c>
@@ -9595,15 +8254,8 @@
       <c r="O191">
         <v>2.5256134203033298E-3</v>
       </c>
-      <c r="P191">
-        <v>9</v>
-      </c>
-      <c r="Q191" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>42309</v>
       </c>
@@ -9640,15 +8292,8 @@
       <c r="O192">
         <v>-8.4611773773675097E-2</v>
       </c>
-      <c r="P192">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="Q192" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>42339</v>
       </c>
@@ -9685,15 +8330,8 @@
       <c r="O193">
         <v>-7.9388116641238696E-2</v>
       </c>
-      <c r="P193">
-        <v>12.9</v>
-      </c>
-      <c r="Q193" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>42370</v>
       </c>
@@ -9730,15 +8368,8 @@
       <c r="O194">
         <v>-4.1030853246836002E-2</v>
       </c>
-      <c r="P194">
-        <v>8.4</v>
-      </c>
-      <c r="Q194" t="str">
-        <f t="shared" si="2"/>
-        <v>2016-Q1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>42401</v>
       </c>
@@ -9775,15 +8406,8 @@
       <c r="O195">
         <v>3.04599438245781E-2</v>
       </c>
-      <c r="P195">
-        <v>8</v>
-      </c>
-      <c r="Q195" t="str">
-        <f t="shared" ref="Q195:Q258" si="3">IF(MONTH($A195) = 1, YEAR($A195)&amp;"-Q"&amp;MONTH($A195), IF(MONTH($A195) = 4, YEAR($A195)&amp;"-Q2", IF(MONTH($A195) = 7, YEAR($A195)&amp;"-Q3", IF(MONTH($A195) = 10, YEAR($A195)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>42430</v>
       </c>
@@ -9820,15 +8444,8 @@
       <c r="O196">
         <v>3.41014506268724E-2</v>
       </c>
-      <c r="P196">
-        <v>5.6</v>
-      </c>
-      <c r="Q196" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>42461</v>
       </c>
@@ -9865,15 +8482,8 @@
       <c r="O197">
         <v>9.19152054803973E-4</v>
       </c>
-      <c r="P197">
-        <v>5.4</v>
-      </c>
-      <c r="Q197" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>42491</v>
       </c>
@@ -9910,15 +8520,8 @@
       <c r="O198">
         <v>-0.101346762169767</v>
       </c>
-      <c r="P198">
-        <v>3.9</v>
-      </c>
-      <c r="Q198" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>42522</v>
       </c>
@@ -9955,15 +8558,8 @@
       <c r="O199">
         <v>5.0624270122389299E-2</v>
       </c>
-      <c r="P199">
-        <v>5.4</v>
-      </c>
-      <c r="Q199" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>42552</v>
       </c>
@@ -10000,15 +8596,8 @@
       <c r="O200">
         <v>1.4979430501467699E-2</v>
       </c>
-      <c r="P200">
-        <v>2.8</v>
-      </c>
-      <c r="Q200" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q3</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>42583</v>
       </c>
@@ -10045,15 +8634,8 @@
       <c r="O201">
         <v>7.1559369889531198E-3</v>
       </c>
-      <c r="P201">
-        <v>5.3</v>
-      </c>
-      <c r="Q201" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>42614</v>
       </c>
@@ -10090,15 +8672,8 @@
       <c r="O202">
         <v>4.0613236594575497E-2</v>
       </c>
-      <c r="P202">
-        <v>5.3</v>
-      </c>
-      <c r="Q202" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>42644</v>
       </c>
@@ -10135,15 +8710,8 @@
       <c r="O203">
         <v>-5.1055543605382801E-2</v>
       </c>
-      <c r="P203">
-        <v>7.3</v>
-      </c>
-      <c r="Q203" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>42675</v>
       </c>
@@ -10180,15 +8748,8 @@
       <c r="O204">
         <v>7.3635069579170306E-2</v>
       </c>
-      <c r="P204">
-        <v>8.5</v>
-      </c>
-      <c r="Q204" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>42705</v>
       </c>
@@ -10225,15 +8786,8 @@
       <c r="O205">
         <v>-3.9533797075765901E-3</v>
       </c>
-      <c r="P205">
-        <v>8.6</v>
-      </c>
-      <c r="Q205" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>42736</v>
       </c>
@@ -10270,15 +8824,8 @@
       <c r="O206">
         <v>2.54694094106576E-2</v>
       </c>
-      <c r="P206">
-        <v>7.9</v>
-      </c>
-      <c r="Q206" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>42767</v>
       </c>
@@ -10315,15 +8862,8 @@
       <c r="O207">
         <v>9.0718799252339694E-2</v>
       </c>
-      <c r="P207">
-        <v>6.1</v>
-      </c>
-      <c r="Q207" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>42795</v>
       </c>
@@ -10360,15 +8900,8 @@
       <c r="O208">
         <v>2.38835654018867E-2</v>
       </c>
-      <c r="P208">
-        <v>8.1</v>
-      </c>
-      <c r="Q208" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>42826</v>
       </c>
@@ -10405,15 +8938,8 @@
       <c r="O209">
         <v>1.5206971826671601E-2</v>
       </c>
-      <c r="P209">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="Q209" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>42856</v>
       </c>
@@ -10450,15 +8976,8 @@
       <c r="O210">
         <v>-4.0850717359223403E-2</v>
       </c>
-      <c r="P210">
-        <v>9.5</v>
-      </c>
-      <c r="Q210" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>42887</v>
       </c>
@@ -10495,15 +9014,8 @@
       <c r="O211">
         <v>5.50925355467413E-3</v>
       </c>
-      <c r="P211">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Q211" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>42917</v>
       </c>
@@ -10540,15 +9052,8 @@
       <c r="O212">
         <v>-1.9489427255260601E-2</v>
       </c>
-      <c r="P212">
-        <v>10.5</v>
-      </c>
-      <c r="Q212" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>42948</v>
       </c>
@@ -10585,15 +9090,8 @@
       <c r="O213">
         <v>7.9300255999026296E-3</v>
       </c>
-      <c r="P213">
-        <v>11.1</v>
-      </c>
-      <c r="Q213" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>42979</v>
       </c>
@@ -10630,15 +9128,8 @@
       <c r="O214">
         <v>1.35854756291991E-2</v>
       </c>
-      <c r="P214">
-        <v>11</v>
-      </c>
-      <c r="Q214" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>43009</v>
       </c>
@@ -10675,15 +9166,8 @@
       <c r="O215">
         <v>-3.0145281023688901E-2</v>
       </c>
-      <c r="P215">
-        <v>10.4</v>
-      </c>
-      <c r="Q215" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>43040</v>
       </c>
@@ -10720,15 +9204,8 @@
       <c r="O216">
         <v>-1.6500046628612701E-2</v>
       </c>
-      <c r="P216">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Q216" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>43070</v>
       </c>
@@ -10765,15 +9242,8 @@
       <c r="O217">
         <v>3.97799848349134E-2</v>
       </c>
-      <c r="P217">
-        <v>10</v>
-      </c>
-      <c r="Q217" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>43101</v>
       </c>
@@ -10810,15 +9280,8 @@
       <c r="O218">
         <v>-6.02593302236318E-2</v>
       </c>
-      <c r="P218">
-        <v>10.3</v>
-      </c>
-      <c r="Q218" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>43132</v>
       </c>
@@ -10855,15 +9318,8 @@
       <c r="O219">
         <v>-2.4681373595235801E-2</v>
       </c>
-      <c r="P219">
-        <v>9.1</v>
-      </c>
-      <c r="Q219" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>43160</v>
       </c>
@@ -10900,15 +9356,8 @@
       <c r="O220">
         <v>3.8838364657442198E-2</v>
       </c>
-      <c r="P220">
-        <v>5.7</v>
-      </c>
-      <c r="Q220" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>43191</v>
       </c>
@@ -10945,15 +9394,8 @@
       <c r="O221">
         <v>-5.2989560150448901E-2</v>
       </c>
-      <c r="P221">
-        <v>7.7</v>
-      </c>
-      <c r="Q221" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>43221</v>
       </c>
@@ -10990,15 +9432,8 @@
       <c r="O222">
         <v>1.6471301408380198E-2</v>
       </c>
-      <c r="P222">
-        <v>8</v>
-      </c>
-      <c r="Q222" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>43252</v>
       </c>
@@ -11035,15 +9470,8 @@
       <c r="O223">
         <v>2.5445881827250699E-2</v>
       </c>
-      <c r="P223">
-        <v>10.8</v>
-      </c>
-      <c r="Q223" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>43282</v>
       </c>
@@ -11080,15 +9508,8 @@
       <c r="O224">
         <v>-4.8956894251995599E-2</v>
       </c>
-      <c r="P224">
-        <v>9.6</v>
-      </c>
-      <c r="Q224" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q3</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>43313</v>
       </c>
@@ -11125,15 +9546,8 @@
       <c r="O225">
         <v>-1.05378507704224E-3</v>
       </c>
-      <c r="P225">
-        <v>8.5</v>
-      </c>
-      <c r="Q225" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>43344</v>
       </c>
@@ -11170,15 +9584,8 @@
       <c r="O226">
         <v>-5.4239440541024898E-2</v>
       </c>
-      <c r="P226">
-        <v>5.5</v>
-      </c>
-      <c r="Q226" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>43374</v>
       </c>
@@ -11215,15 +9622,8 @@
       <c r="O227">
         <v>2.0445123696758199E-2</v>
       </c>
-      <c r="P227">
-        <v>6.1</v>
-      </c>
-      <c r="Q227" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>43405</v>
       </c>
@@ -11260,15 +9660,8 @@
       <c r="O228">
         <v>-6.1016452658940103E-2</v>
       </c>
-      <c r="P228">
-        <v>7.6</v>
-      </c>
-      <c r="Q228" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>43435</v>
       </c>
@@ -11305,15 +9698,8 @@
       <c r="O229">
         <v>5.8755492987682303E-2</v>
       </c>
-      <c r="P229">
-        <v>6.2</v>
-      </c>
-      <c r="Q229" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>43466</v>
       </c>
@@ -11350,15 +9736,8 @@
       <c r="O230">
         <v>2.41088554448456E-2</v>
       </c>
-      <c r="P230">
-        <v>6.8</v>
-      </c>
-      <c r="Q230" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>43497</v>
       </c>
@@ -11395,15 +9774,8 @@
       <c r="O231">
         <v>-4.03936078176947E-3</v>
       </c>
-      <c r="P231">
-        <v>7</v>
-      </c>
-      <c r="Q231" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>43525</v>
       </c>
@@ -11440,15 +9812,8 @@
       <c r="O232">
         <v>3.5121527087246897E-2</v>
       </c>
-      <c r="P232">
-        <v>10.7</v>
-      </c>
-      <c r="Q232" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>43556</v>
       </c>
@@ -11485,15 +9850,8 @@
       <c r="O233">
         <v>-6.1004701770091402E-2</v>
       </c>
-      <c r="P233">
-        <v>6.5</v>
-      </c>
-      <c r="Q233" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>43586</v>
       </c>
@@ -11530,15 +9888,8 @@
       <c r="O234">
         <v>2.1381862693512901E-2</v>
       </c>
-      <c r="P234">
-        <v>8.1</v>
-      </c>
-      <c r="Q234" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>43617</v>
       </c>
@@ -11575,15 +9926,8 @@
       <c r="O235">
         <v>-2.5075866955493398E-2</v>
       </c>
-      <c r="P235">
-        <v>10.6</v>
-      </c>
-      <c r="Q235" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>43647</v>
       </c>
@@ -11620,15 +9964,8 @@
       <c r="O236">
         <v>-1.7780551073707698E-2</v>
       </c>
-      <c r="P236">
-        <v>6.4</v>
-      </c>
-      <c r="Q236" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q3</v>
-      </c>
-    </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>43678</v>
       </c>
@@ -11665,15 +10002,8 @@
       <c r="O237">
         <v>4.7822953514613097E-2</v>
       </c>
-      <c r="P237">
-        <v>5.9</v>
-      </c>
-      <c r="Q237" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>43709</v>
       </c>
@@ -11710,15 +10040,8 @@
       <c r="O238">
         <v>1.39447878757792E-3</v>
       </c>
-      <c r="P238">
-        <v>4.8</v>
-      </c>
-      <c r="Q238" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>43739</v>
       </c>
@@ -11755,15 +10078,8 @@
       <c r="O239">
         <v>1.01561903641372E-2</v>
       </c>
-      <c r="P239">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="Q239" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>43770</v>
       </c>
@@ -11800,15 +10116,8 @@
       <c r="O240">
         <v>2.08671776337752E-2</v>
       </c>
-      <c r="P240">
-        <v>2.1</v>
-      </c>
-      <c r="Q240" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>43800</v>
       </c>
@@ -11845,15 +10154,8 @@
       <c r="O241">
         <v>-1.9168408503917399E-2</v>
       </c>
-      <c r="P241">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="Q241" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>43831</v>
       </c>
@@ -11890,15 +10192,8 @@
       <c r="O242">
         <v>-7.1302827829598001E-2</v>
       </c>
-      <c r="P242">
-        <v>1</v>
-      </c>
-      <c r="Q242" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>43862</v>
       </c>
@@ -11935,15 +10230,8 @@
       <c r="O243">
         <v>-0.25121293473894102</v>
       </c>
-      <c r="P243">
-        <v>4</v>
-      </c>
-      <c r="Q243" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>43891</v>
       </c>
@@ -11980,15 +10268,8 @@
       <c r="O244">
         <v>1.9974825403062699E-2</v>
       </c>
-      <c r="P244">
-        <v>0.6</v>
-      </c>
-      <c r="Q244" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>43922</v>
       </c>
@@ -12025,15 +10306,8 @@
       <c r="O245">
         <v>2.48536486230275E-2</v>
       </c>
-      <c r="P245">
-        <v>-20.9</v>
-      </c>
-      <c r="Q245" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q2</v>
-      </c>
-    </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>43952</v>
       </c>
@@ -12070,15 +10344,8 @@
       <c r="O246">
         <v>1.8830936784702601E-2</v>
       </c>
-      <c r="P246">
-        <v>-19</v>
-      </c>
-      <c r="Q246" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>43983</v>
       </c>
@@ -12115,15 +10382,8 @@
       <c r="O247">
         <v>-5.0191982197796699E-2</v>
       </c>
-      <c r="P247">
-        <v>-12.4</v>
-      </c>
-      <c r="Q247" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>44013</v>
       </c>
@@ -12160,15 +10420,8 @@
       <c r="O248">
         <v>1.33028268437219E-2</v>
       </c>
-      <c r="P248">
-        <v>-12.9</v>
-      </c>
-      <c r="Q248" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>44044</v>
       </c>
@@ -12205,15 +10458,8 @@
       <c r="O249">
         <v>-3.6961397531255699E-2</v>
       </c>
-      <c r="P249">
-        <v>-15.4</v>
-      </c>
-      <c r="Q249" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>44075</v>
       </c>
@@ -12250,15 +10496,8 @@
       <c r="O250">
         <v>-4.0160900463224201E-2</v>
       </c>
-      <c r="P250">
-        <v>-13.6</v>
-      </c>
-      <c r="Q250" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>44105</v>
       </c>
@@ -12295,15 +10534,8 @@
       <c r="O251">
         <v>0.22458693526491499</v>
       </c>
-      <c r="P251">
-        <v>-13.2</v>
-      </c>
-      <c r="Q251" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>44136</v>
       </c>
@@ -12340,15 +10572,8 @@
       <c r="O252">
         <v>-3.9623383078790701E-4</v>
       </c>
-      <c r="P252">
-        <v>-13.9</v>
-      </c>
-      <c r="Q252" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>44166</v>
       </c>
@@ -12385,15 +10610,8 @@
       <c r="O253">
         <v>-3.9951772287052399E-2</v>
       </c>
-      <c r="P253">
-        <v>-7.2</v>
-      </c>
-      <c r="Q253" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>44197</v>
       </c>
@@ -12430,15 +10648,8 @@
       <c r="O254">
         <v>5.8518179311036499E-2</v>
       </c>
-      <c r="P254">
-        <v>-8.6</v>
-      </c>
-      <c r="Q254" t="str">
-        <f t="shared" si="3"/>
-        <v>2021-Q1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>44228</v>
       </c>
@@ -12475,15 +10686,8 @@
       <c r="O255">
         <v>4.2255616848436303E-2</v>
       </c>
-      <c r="P255">
-        <v>-10.3</v>
-      </c>
-      <c r="Q255" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>44256</v>
       </c>
@@ -12520,15 +10724,8 @@
       <c r="O256">
         <v>2.70209023499621E-2</v>
       </c>
-      <c r="P256">
-        <v>-1.2</v>
-      </c>
-      <c r="Q256" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>44287</v>
       </c>
@@ -12565,15 +10762,8 @@
       <c r="O257">
         <v>3.71788803279181E-2</v>
       </c>
-      <c r="P257">
-        <v>-0.6</v>
-      </c>
-      <c r="Q257" t="str">
-        <f t="shared" si="3"/>
-        <v>2021-Q2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>44317</v>
       </c>
@@ -12610,15 +10800,8 @@
       <c r="O258">
         <v>-3.6475758850585301E-2</v>
       </c>
-      <c r="P258">
-        <v>1.7</v>
-      </c>
-      <c r="Q258" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>44348</v>
       </c>
@@ -12655,15 +10838,8 @@
       <c r="O259">
         <v>-1.6631900594395801E-2</v>
       </c>
-      <c r="P259">
-        <v>2.8</v>
-      </c>
-      <c r="Q259" t="str">
-        <f t="shared" ref="Q259:Q313" si="4">IF(MONTH($A259) = 1, YEAR($A259)&amp;"-Q"&amp;MONTH($A259), IF(MONTH($A259) = 4, YEAR($A259)&amp;"-Q2", IF(MONTH($A259) = 7, YEAR($A259)&amp;"-Q3", IF(MONTH($A259) = 10, YEAR($A259)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>44378</v>
       </c>
@@ -12700,15 +10876,8 @@
       <c r="O260">
         <v>1.95071235243773E-2</v>
       </c>
-      <c r="P260">
-        <v>3</v>
-      </c>
-      <c r="Q260" t="str">
-        <f t="shared" si="4"/>
-        <v>2021-Q3</v>
-      </c>
-    </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>44409</v>
       </c>
@@ -12745,15 +10914,8 @@
       <c r="O261">
         <v>-5.7020039381754399E-3</v>
       </c>
-      <c r="P261">
-        <v>3.9</v>
-      </c>
-      <c r="Q261" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>44440</v>
       </c>
@@ -12790,15 +10952,8 @@
       <c r="O262">
         <v>2.9284089935702098E-2</v>
       </c>
-      <c r="P262">
-        <v>3.3</v>
-      </c>
-      <c r="Q262" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>44470</v>
       </c>
@@ -12835,15 +10990,8 @@
       <c r="O263">
         <v>-8.6745509357067305E-2</v>
       </c>
-      <c r="P263">
-        <v>4.8</v>
-      </c>
-      <c r="Q263" t="str">
-        <f t="shared" si="4"/>
-        <v>2021-Q4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>44501</v>
       </c>
@@ -12880,15 +11028,8 @@
       <c r="O264">
         <v>4.8038216547910302E-2</v>
       </c>
-      <c r="P264">
-        <v>-2.4</v>
-      </c>
-      <c r="Q264" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>44531</v>
       </c>
@@ -12925,15 +11066,8 @@
       <c r="O265">
         <v>-1.1658507297965999E-2</v>
       </c>
-      <c r="P265">
-        <v>-2</v>
-      </c>
-      <c r="Q265" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>44562</v>
       </c>
@@ -12970,15 +11104,8 @@
       <c r="O266">
         <v>-1.5633317382336601E-2</v>
       </c>
-      <c r="P266">
-        <v>-1.2</v>
-      </c>
-      <c r="Q266" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>44593</v>
       </c>
@@ -13015,15 +11142,8 @@
       <c r="O267">
         <v>-4.0297835039648797E-3</v>
       </c>
-      <c r="P267">
-        <v>1.4</v>
-      </c>
-      <c r="Q267" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>44621</v>
       </c>
@@ -13060,15 +11180,8 @@
       <c r="O268">
         <v>1.6336981709512699E-2</v>
       </c>
-      <c r="P268">
-        <v>-16.899999999999999</v>
-      </c>
-      <c r="Q268" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>44652</v>
       </c>
@@ -13105,15 +11218,8 @@
       <c r="O269">
         <v>3.0663609212433902E-2</v>
       </c>
-      <c r="P269">
-        <v>-14.9</v>
-      </c>
-      <c r="Q269" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>44682</v>
       </c>
@@ -13150,15 +11256,8 @@
       <c r="O270">
         <v>-8.8883357095952006E-2</v>
       </c>
-      <c r="P270">
-        <v>-11.2</v>
-      </c>
-      <c r="Q270" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>44713</v>
       </c>
@@ -13195,15 +11294,8 @@
       <c r="O271">
         <v>7.0748190952389899E-3</v>
       </c>
-      <c r="P271">
-        <v>-17.100000000000001</v>
-      </c>
-      <c r="Q271" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>44743</v>
       </c>
@@ -13240,15 +11332,8 @@
       <c r="O272">
         <v>-3.3676669724133697E-2</v>
       </c>
-      <c r="P272">
-        <v>-23.7</v>
-      </c>
-      <c r="Q272" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q3</v>
-      </c>
-    </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>44774</v>
       </c>
@@ -13285,15 +11370,8 @@
       <c r="O273">
         <v>-6.8118335731565297E-2</v>
       </c>
-      <c r="P273">
-        <v>-19.5</v>
-      </c>
-      <c r="Q273" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>44805</v>
       </c>
@@ -13330,15 +11408,8 @@
       <c r="O274">
         <v>7.7005811941317504E-2</v>
       </c>
-      <c r="P274">
-        <v>-19.8</v>
-      </c>
-      <c r="Q274" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>44835</v>
       </c>
@@ -13375,15 +11446,8 @@
       <c r="O275">
         <v>4.9851947662217497E-2</v>
       </c>
-      <c r="P275">
-        <v>-18.5</v>
-      </c>
-      <c r="Q275" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q4</v>
-      </c>
-    </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>44866</v>
       </c>
@@ -13420,15 +11484,8 @@
       <c r="O276">
         <v>-1.6164547104466499E-2</v>
       </c>
-      <c r="P276">
-        <v>-15.2</v>
-      </c>
-      <c r="Q276" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>44896</v>
       </c>
@@ -13465,15 +11522,8 @@
       <c r="O277">
         <v>9.3318632006559099E-2</v>
       </c>
-      <c r="P277">
-        <v>-12.6</v>
-      </c>
-      <c r="Q277" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>44927</v>
       </c>
@@ -13510,15 +11560,8 @@
       <c r="O278">
         <v>3.9139777308690803E-2</v>
       </c>
-      <c r="P278">
-        <v>-10.199999999999999</v>
-      </c>
-      <c r="Q278" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>44958</v>
       </c>
@@ -13555,15 +11598,8 @@
       <c r="O279">
         <v>-1.7405146796521699E-2</v>
       </c>
-      <c r="P279">
-        <v>-9</v>
-      </c>
-      <c r="Q279" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>44986</v>
       </c>
@@ -13600,15 +11636,8 @@
       <c r="O280">
         <v>9.2023716132238998E-4</v>
       </c>
-      <c r="P280">
-        <v>-11.5</v>
-      </c>
-      <c r="Q280" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>45017</v>
       </c>
@@ -13645,15 +11674,8 @@
       <c r="O281">
         <v>-2.0863226409730401E-2</v>
       </c>
-      <c r="P281">
-        <v>-7.6</v>
-      </c>
-      <c r="Q281" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>45047</v>
       </c>
@@ -13690,15 +11712,8 @@
       <c r="O282">
         <v>5.82467873396375E-2</v>
       </c>
-      <c r="P282">
-        <v>-8.1999999999999993</v>
-      </c>
-      <c r="Q282" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>45078</v>
       </c>
@@ -13735,15 +11750,8 @@
       <c r="O283">
         <v>5.0430323417121102E-3</v>
       </c>
-      <c r="P283">
-        <v>-4.2</v>
-      </c>
-      <c r="Q283" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>45108</v>
       </c>
@@ -13780,15 +11788,8 @@
       <c r="O284">
         <v>-1.4163998619924499E-2</v>
       </c>
-      <c r="P284">
-        <v>0</v>
-      </c>
-      <c r="Q284" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q3</v>
-      </c>
-    </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>45139</v>
       </c>
@@ -13825,15 +11826,8 @@
       <c r="O285">
         <v>-8.2287144837138709E-3</v>
       </c>
-      <c r="P285">
-        <v>-2.9</v>
-      </c>
-      <c r="Q285" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>45170</v>
       </c>
@@ -13870,15 +11864,8 @@
       <c r="O286">
         <v>-4.45390522802427E-2</v>
       </c>
-      <c r="P286">
-        <v>-8.1</v>
-      </c>
-      <c r="Q286" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>45200</v>
       </c>
@@ -13915,15 +11902,8 @@
       <c r="O287">
         <v>0.10924330884559</v>
       </c>
-      <c r="P287">
-        <v>-7.1</v>
-      </c>
-      <c r="Q287" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>45231</v>
       </c>
@@ -13960,15 +11940,8 @@
       <c r="O288">
         <v>4.3550427198262298E-3</v>
       </c>
-      <c r="P288">
-        <v>-6.9</v>
-      </c>
-      <c r="Q288" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>45261</v>
       </c>
@@ -14005,15 +11978,8 @@
       <c r="O289">
         <v>-2.41820297413398E-3</v>
       </c>
-      <c r="P289">
-        <v>-6.2</v>
-      </c>
-      <c r="Q289" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>45292</v>
       </c>
@@ -14050,15 +12016,8 @@
       <c r="O290">
         <v>-7.6100163688579397E-3</v>
       </c>
-      <c r="P290">
-        <v>-6.6</v>
-      </c>
-      <c r="Q290" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>45323</v>
       </c>
@@ -14095,15 +12054,8 @@
       <c r="O291">
         <v>0.10193909760924</v>
       </c>
-      <c r="P291">
-        <v>-4.8</v>
-      </c>
-      <c r="Q291" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>45352</v>
       </c>
@@ -14140,15 +12092,8 @@
       <c r="O292">
         <v>-2.0083598902259001E-2</v>
       </c>
-      <c r="P292">
-        <v>-3.2</v>
-      </c>
-      <c r="Q292" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>45383</v>
       </c>
@@ -14185,15 +12130,8 @@
       <c r="O293">
         <v>4.2177171891420798E-2</v>
       </c>
-      <c r="P293">
-        <v>-2</v>
-      </c>
-      <c r="Q293" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q2</v>
-      </c>
-    </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>45413</v>
       </c>
@@ -14230,15 +12168,8 @@
       <c r="O294">
         <v>-3.3983769543672403E-2</v>
       </c>
-      <c r="P294">
-        <v>-2.1</v>
-      </c>
-      <c r="Q294" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>45444</v>
       </c>
@@ -14275,15 +12206,8 @@
       <c r="O295">
         <v>1.10230074322182E-2</v>
       </c>
-      <c r="P295">
-        <v>-2</v>
-      </c>
-      <c r="Q295" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>45474</v>
       </c>
@@ -14320,15 +12244,8 @@
       <c r="O296">
         <v>2.9993068936397201E-2</v>
       </c>
-      <c r="P296">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="Q296" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q3</v>
-      </c>
-    </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>45505</v>
       </c>
@@ -14365,15 +12282,8 @@
       <c r="O297">
         <v>4.0848956493272602E-2</v>
       </c>
-      <c r="P297">
-        <v>-2.8</v>
-      </c>
-      <c r="Q297" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>45536</v>
       </c>
@@ -14410,15 +12320,8 @@
       <c r="O298">
         <v>-1.7384817426551201E-2</v>
       </c>
-      <c r="P298">
-        <v>0.1</v>
-      </c>
-      <c r="Q298" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>45566</v>
       </c>
@@ -14455,15 +12358,8 @@
       <c r="O299">
         <v>-2.6850783677705402E-3</v>
       </c>
-      <c r="P299">
-        <v>-0.3</v>
-      </c>
-      <c r="Q299" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q4</v>
-      </c>
-    </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>45597</v>
       </c>
@@ -14500,15 +12396,8 @@
       <c r="O300">
         <v>-3.9851324308663996E-3</v>
       </c>
-      <c r="P300">
-        <v>0.8</v>
-      </c>
-      <c r="Q300" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>45627</v>
       </c>
@@ -14545,15 +12434,8 @@
       <c r="O301">
         <v>6.4611318505971099E-2</v>
       </c>
-      <c r="P301">
-        <v>1.9</v>
-      </c>
-      <c r="Q301" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>45658</v>
       </c>
@@ -14590,15 +12472,8 @@
       <c r="O302">
         <v>7.6128813353950206E-2</v>
       </c>
-      <c r="P302">
-        <v>0.6</v>
-      </c>
-      <c r="Q302" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>45689</v>
       </c>
@@ -14635,15 +12510,8 @@
       <c r="O303">
         <v>-1.6003197167055599E-2</v>
       </c>
-      <c r="P303">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="Q303" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>45717</v>
       </c>
@@ -14680,15 +12548,8 @@
       <c r="O304">
         <v>1.15354009247373E-2</v>
       </c>
-      <c r="P304">
-        <v>-2</v>
-      </c>
-      <c r="Q304" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>45748</v>
       </c>
@@ -14725,15 +12586,8 @@
       <c r="O305">
         <v>6.3023796511506802E-2</v>
       </c>
-      <c r="P305">
-        <v>-4.5</v>
-      </c>
-      <c r="Q305" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q2</v>
-      </c>
-    </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>45778</v>
       </c>
@@ -14770,15 +12624,8 @@
       <c r="O306">
         <v>-1.13914841690139E-2</v>
       </c>
-      <c r="P306">
-        <v>-2.5</v>
-      </c>
-      <c r="Q306" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>45809</v>
       </c>
@@ -14815,15 +12662,8 @@
       <c r="O307">
         <v>2.8541232876627E-2</v>
       </c>
-      <c r="P307">
-        <v>-3.2</v>
-      </c>
-      <c r="Q307" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>45839</v>
       </c>
@@ -14860,15 +12700,8 @@
       <c r="O308">
         <v>3.6741151062759797E-2</v>
       </c>
-      <c r="P308">
-        <v>-4.5999999999999996</v>
-      </c>
-      <c r="Q308" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q3</v>
-      </c>
-    </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>45870</v>
       </c>
@@ -14905,15 +12738,8 @@
       <c r="O309">
         <v>3.5464815963681701E-2</v>
       </c>
-      <c r="P309">
-        <v>-2.6</v>
-      </c>
-      <c r="Q309" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>45901</v>
       </c>
@@ -14950,15 +12776,8 @@
       <c r="O310">
         <v>3.5398306416771802E-2</v>
       </c>
-      <c r="P310">
-        <v>-0.8</v>
-      </c>
-      <c r="Q310" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>45931</v>
       </c>
@@ -14995,15 +12814,8 @@
       <c r="O311">
         <v>2.0923977527344199E-2</v>
       </c>
-      <c r="P311">
-        <v>0</v>
-      </c>
-      <c r="Q311" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q4</v>
-      </c>
-    </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>45962</v>
       </c>
@@ -15040,15 +12852,8 @@
       <c r="O312">
         <v>5.5609209569579897E-2</v>
       </c>
-      <c r="P312">
-        <v>-0.7</v>
-      </c>
-      <c r="Q312" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>45992</v>
       </c>
@@ -15084,13 +12889,6 @@
       </c>
       <c r="O313">
         <v>1.9844680546508901E-2</v>
-      </c>
-      <c r="P313">
-        <v>-1.7</v>
-      </c>
-      <c r="Q313" t="str">
-        <f t="shared" si="4"/>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -15102,41 +12900,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D49BF3C-99BE-B04B-9A3C-656750B962CB}">
   <dimension ref="A1:Q314"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>5</v>
@@ -15148,16 +12946,16 @@
         <v>3</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>36526</v>
       </c>
@@ -15201,7 +12999,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>36557</v>
       </c>
@@ -15245,7 +13043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>36586</v>
       </c>
@@ -15289,7 +13087,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>36617</v>
       </c>
@@ -15333,7 +13131,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>36647</v>
       </c>
@@ -15377,7 +13175,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>36678</v>
       </c>
@@ -15421,7 +13219,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>36708</v>
       </c>
@@ -15465,7 +13263,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>36739</v>
       </c>
@@ -15509,7 +13307,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>36770</v>
       </c>
@@ -15550,10 +13348,10 @@
         <v>61.95</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>36800</v>
       </c>
@@ -15597,7 +13395,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>36831</v>
       </c>
@@ -15641,7 +13439,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>36861</v>
       </c>
@@ -15685,7 +13483,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>36892</v>
       </c>
@@ -15729,7 +13527,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>36923</v>
       </c>
@@ -15773,7 +13571,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>36951</v>
       </c>
@@ -15817,7 +13615,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>36982</v>
       </c>
@@ -15861,7 +13659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>37012</v>
       </c>
@@ -15905,7 +13703,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>37043</v>
       </c>
@@ -15949,7 +13747,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>37073</v>
       </c>
@@ -15993,7 +13791,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>37104</v>
       </c>
@@ -16037,7 +13835,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>37135</v>
       </c>
@@ -16078,10 +13876,10 @@
         <v>60.21</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>37165</v>
       </c>
@@ -16125,7 +13923,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>37196</v>
       </c>
@@ -16169,7 +13967,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>37226</v>
       </c>
@@ -16213,10 +14011,10 @@
         <v>56.75</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>37257</v>
       </c>
@@ -16263,7 +14061,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>37288</v>
       </c>
@@ -16310,7 +14108,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>37316</v>
       </c>
@@ -16357,7 +14155,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>37347</v>
       </c>
@@ -16404,7 +14202,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>37377</v>
       </c>
@@ -16451,7 +14249,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>37408</v>
       </c>
@@ -16498,7 +14296,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>37438</v>
       </c>
@@ -16545,7 +14343,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>37469</v>
       </c>
@@ -16592,7 +14390,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>37500</v>
       </c>
@@ -16639,7 +14437,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>37530</v>
       </c>
@@ -16686,7 +14484,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>37561</v>
       </c>
@@ -16733,7 +14531,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>37591</v>
       </c>
@@ -16780,7 +14578,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37622</v>
       </c>
@@ -16827,7 +14625,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>37653</v>
       </c>
@@ -16874,7 +14672,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>37681</v>
       </c>
@@ -16921,7 +14719,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>37712</v>
       </c>
@@ -16968,7 +14766,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>37742</v>
       </c>
@@ -17015,7 +14813,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>37773</v>
       </c>
@@ -17062,7 +14860,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>37803</v>
       </c>
@@ -17106,10 +14904,10 @@
         <v>60.06</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>37834</v>
       </c>
@@ -17156,7 +14954,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>37865</v>
       </c>
@@ -17203,7 +15001,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>37895</v>
       </c>
@@ -17250,7 +15048,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>37926</v>
       </c>
@@ -17297,7 +15095,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>37956</v>
       </c>
@@ -17341,10 +15139,10 @@
         <v>59.96</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>37987</v>
       </c>
@@ -17391,7 +15189,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>38018</v>
       </c>
@@ -17438,7 +15236,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>38047</v>
       </c>
@@ -17485,7 +15283,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>38078</v>
       </c>
@@ -17532,7 +15330,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>38108</v>
       </c>
@@ -17579,7 +15377,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>38139</v>
       </c>
@@ -17626,7 +15424,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>38169</v>
       </c>
@@ -17673,7 +15471,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>38200</v>
       </c>
@@ -17720,7 +15518,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>38231</v>
       </c>
@@ -17767,7 +15565,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>38261</v>
       </c>
@@ -17814,7 +15612,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>38292</v>
       </c>
@@ -17861,7 +15659,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>38322</v>
       </c>
@@ -17905,10 +15703,10 @@
         <v>64.5</v>
       </c>
       <c r="Q61" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>38353</v>
       </c>
@@ -17955,7 +15753,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>38384</v>
       </c>
@@ -18002,7 +15800,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>38412</v>
       </c>
@@ -18049,7 +15847,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>38443</v>
       </c>
@@ -18096,7 +15894,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>38473</v>
       </c>
@@ -18143,7 +15941,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>38504</v>
       </c>
@@ -18190,7 +15988,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>38534</v>
       </c>
@@ -18237,7 +16035,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>38565</v>
       </c>
@@ -18284,7 +16082,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>38596</v>
       </c>
@@ -18331,7 +16129,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>38626</v>
       </c>
@@ -18378,7 +16176,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>38657</v>
       </c>
@@ -18422,10 +16220,10 @@
         <v>72.28</v>
       </c>
       <c r="Q72" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>38687</v>
       </c>
@@ -18472,7 +16270,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>38718</v>
       </c>
@@ -18519,7 +16317,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>38749</v>
       </c>
@@ -18566,7 +16364,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>38777</v>
       </c>
@@ -18613,7 +16411,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>38808</v>
       </c>
@@ -18660,7 +16458,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>38838</v>
       </c>
@@ -18707,7 +16505,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>38869</v>
       </c>
@@ -18754,7 +16552,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>38899</v>
       </c>
@@ -18801,7 +16599,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>38930</v>
       </c>
@@ -18848,7 +16646,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>38961</v>
       </c>
@@ -18895,7 +16693,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>38991</v>
       </c>
@@ -18942,7 +16740,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>39022</v>
       </c>
@@ -18989,7 +16787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>39052</v>
       </c>
@@ -19036,7 +16834,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>39083</v>
       </c>
@@ -19083,7 +16881,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>39114</v>
       </c>
@@ -19130,7 +16928,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>39142</v>
       </c>
@@ -19177,7 +16975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>39173</v>
       </c>
@@ -19224,7 +17022,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>39203</v>
       </c>
@@ -19271,7 +17069,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>39234</v>
       </c>
@@ -19318,7 +17116,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>39264</v>
       </c>
@@ -19365,7 +17163,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>39295</v>
       </c>
@@ -19412,7 +17210,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>39326</v>
       </c>
@@ -19459,7 +17257,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>39356</v>
       </c>
@@ -19506,7 +17304,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>39387</v>
       </c>
@@ -19553,7 +17351,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>39417</v>
       </c>
@@ -19600,7 +17398,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>39448</v>
       </c>
@@ -19647,7 +17445,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>39479</v>
       </c>
@@ -19694,7 +17492,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>39508</v>
       </c>
@@ -19741,7 +17539,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>39539</v>
       </c>
@@ -19788,7 +17586,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>39569</v>
       </c>
@@ -19835,7 +17633,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>39600</v>
       </c>
@@ -19882,7 +17680,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>39630</v>
       </c>
@@ -19929,7 +17727,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>39661</v>
       </c>
@@ -19976,7 +17774,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>39692</v>
       </c>
@@ -20023,7 +17821,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>39722</v>
       </c>
@@ -20070,7 +17868,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>39753</v>
       </c>
@@ -20117,7 +17915,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>39783</v>
       </c>
@@ -20164,7 +17962,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>39814</v>
       </c>
@@ -20208,10 +18006,10 @@
         <v>74.709999999999994</v>
       </c>
       <c r="Q110" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>39845</v>
       </c>
@@ -20258,7 +18056,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>39873</v>
       </c>
@@ -20305,7 +18103,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>39904</v>
       </c>
@@ -20352,7 +18150,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>39934</v>
       </c>
@@ -20399,7 +18197,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>39965</v>
       </c>
@@ -20446,7 +18244,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>39995</v>
       </c>
@@ -20493,7 +18291,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>40026</v>
       </c>
@@ -20540,7 +18338,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>40057</v>
       </c>
@@ -20587,7 +18385,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>40087</v>
       </c>
@@ -20634,7 +18432,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>40118</v>
       </c>
@@ -20681,7 +18479,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>40148</v>
       </c>
@@ -20725,10 +18523,10 @@
         <v>80.89</v>
       </c>
       <c r="Q121" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>40179</v>
       </c>
@@ -20775,7 +18573,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>40210</v>
       </c>
@@ -20822,7 +18620,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>40238</v>
       </c>
@@ -20869,7 +18667,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>40269</v>
       </c>
@@ -20913,10 +18711,10 @@
         <v>87.52</v>
       </c>
       <c r="Q125" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>40299</v>
       </c>
@@ -20960,10 +18758,10 @@
         <v>88.09</v>
       </c>
       <c r="Q126" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>40330</v>
       </c>
@@ -21007,10 +18805,10 @@
         <v>87.63</v>
       </c>
       <c r="Q127" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>40360</v>
       </c>
@@ -21057,7 +18855,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>40391</v>
       </c>
@@ -21104,7 +18902,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>40422</v>
       </c>
@@ -21148,10 +18946,10 @@
         <v>88.67</v>
       </c>
       <c r="Q130" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>40452</v>
       </c>
@@ -21198,7 +18996,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>40483</v>
       </c>
@@ -21245,7 +19043,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>40513</v>
       </c>
@@ -21289,10 +19087,10 @@
         <v>93.48</v>
       </c>
       <c r="Q133" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>40544</v>
       </c>
@@ -21339,7 +19137,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>40575</v>
       </c>
@@ -21386,7 +19184,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>40603</v>
       </c>
@@ -21412,7 +19210,7 @@
         <v>#N/A</v>
       </c>
       <c r="I136">
-        <v>0.13974380493164063</v>
+        <v>0.13974380493164062</v>
       </c>
       <c r="L136">
         <v>102.9</v>
@@ -21430,10 +19228,10 @@
         <v>101.26</v>
       </c>
       <c r="Q136" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>40634</v>
       </c>
@@ -21480,7 +19278,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>40664</v>
       </c>
@@ -21527,7 +19325,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>40695</v>
       </c>
@@ -21574,7 +19372,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>40725</v>
       </c>
@@ -21618,10 +19416,10 @@
         <v>102.72</v>
       </c>
       <c r="Q140" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>40756</v>
       </c>
@@ -21668,7 +19466,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>40787</v>
       </c>
@@ -21715,7 +19513,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>40817</v>
       </c>
@@ -21759,10 +19557,10 @@
         <v>102.87</v>
       </c>
       <c r="Q143" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>40848</v>
       </c>
@@ -21806,10 +19604,10 @@
         <v>103.43</v>
       </c>
       <c r="Q144" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>40878</v>
       </c>
@@ -21853,10 +19651,10 @@
         <v>103.13</v>
       </c>
       <c r="Q145" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>40909</v>
       </c>
@@ -21900,10 +19698,10 @@
         <v>105.52</v>
       </c>
       <c r="Q146" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>40940</v>
       </c>
@@ -21947,10 +19745,10 @@
         <v>106.66</v>
       </c>
       <c r="Q147" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>40969</v>
       </c>
@@ -21997,7 +19795,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>41000</v>
       </c>
@@ -22041,10 +19839,10 @@
         <v>112.07</v>
       </c>
       <c r="Q149" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>41030</v>
       </c>
@@ -22091,7 +19889,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>41061</v>
       </c>
@@ -22135,10 +19933,10 @@
         <v>107.36</v>
       </c>
       <c r="Q151" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>41091</v>
       </c>
@@ -22185,7 +19983,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>41122</v>
       </c>
@@ -22232,7 +20030,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>41153</v>
       </c>
@@ -22279,7 +20077,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>41183</v>
       </c>
@@ -22323,10 +20121,10 @@
         <v>114.38</v>
       </c>
       <c r="Q155" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>41214</v>
       </c>
@@ -22373,7 +20171,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>41244</v>
       </c>
@@ -22420,7 +20218,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>41275</v>
       </c>
@@ -22467,7 +20265,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>41306</v>
       </c>
@@ -22514,7 +20312,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>41334</v>
       </c>
@@ -22558,10 +20356,10 @@
         <v>112.32</v>
       </c>
       <c r="Q160" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>41365</v>
       </c>
@@ -22608,7 +20406,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>41395</v>
       </c>
@@ -22652,10 +20450,10 @@
         <v>108.01</v>
       </c>
       <c r="Q162" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>41426</v>
       </c>
@@ -22702,7 +20500,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>41456</v>
       </c>
@@ -22746,10 +20544,10 @@
         <v>110.29</v>
       </c>
       <c r="Q164" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>41487</v>
       </c>
@@ -22796,7 +20594,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>41518</v>
       </c>
@@ -22840,10 +20638,10 @@
         <v>112.12</v>
       </c>
       <c r="Q166" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>41548</v>
       </c>
@@ -22887,10 +20685,10 @@
         <v>111.25</v>
       </c>
       <c r="Q167" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>41579</v>
       </c>
@@ -22934,10 +20732,10 @@
         <v>110.43</v>
       </c>
       <c r="Q168" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>41609</v>
       </c>
@@ -22981,10 +20779,10 @@
         <v>111.15</v>
       </c>
       <c r="Q169" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>41640</v>
       </c>
@@ -23028,10 +20826,10 @@
         <v>111.11</v>
       </c>
       <c r="Q170" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>41671</v>
       </c>
@@ -23075,10 +20873,10 @@
         <v>111.1</v>
       </c>
       <c r="Q171" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>41699</v>
       </c>
@@ -23122,10 +20920,10 @@
         <v>110.72</v>
       </c>
       <c r="Q172" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>41730</v>
       </c>
@@ -23169,10 +20967,10 @@
         <v>111</v>
       </c>
       <c r="Q173" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>41760</v>
       </c>
@@ -23216,10 +21014,10 @@
         <v>111.21</v>
       </c>
       <c r="Q174" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>41791</v>
       </c>
@@ -23266,7 +21064,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>41821</v>
       </c>
@@ -23310,10 +21108,10 @@
         <v>110.61</v>
       </c>
       <c r="Q176" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>41852</v>
       </c>
@@ -23357,10 +21155,10 @@
         <v>110.59</v>
       </c>
       <c r="Q177" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>41883</v>
       </c>
@@ -23404,10 +21202,10 @@
         <v>112.1</v>
       </c>
       <c r="Q178" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>41913</v>
       </c>
@@ -23451,10 +21249,10 @@
         <v>110</v>
       </c>
       <c r="Q179" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>41944</v>
       </c>
@@ -23501,7 +21299,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>41974</v>
       </c>
@@ -23548,7 +21346,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>42005</v>
       </c>
@@ -23595,7 +21393,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>42036</v>
       </c>
@@ -23642,7 +21440,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>42064</v>
       </c>
@@ -23689,7 +21487,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>42095</v>
       </c>
@@ -23736,7 +21534,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>42125</v>
       </c>
@@ -23783,7 +21581,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>42156</v>
       </c>
@@ -23830,7 +21628,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>42186</v>
       </c>
@@ -23877,7 +21675,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>42217</v>
       </c>
@@ -23924,7 +21722,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>42248</v>
       </c>
@@ -23971,7 +21769,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>42278</v>
       </c>
@@ -24015,10 +21813,10 @@
         <v>95.63</v>
       </c>
       <c r="Q191" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>42309</v>
       </c>
@@ -24065,7 +21863,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>42339</v>
       </c>
@@ -24112,7 +21910,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>42370</v>
       </c>
@@ -24156,10 +21954,10 @@
         <v>88.35</v>
       </c>
       <c r="Q194" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>42401</v>
       </c>
@@ -24203,10 +22001,10 @@
         <v>85.8</v>
       </c>
       <c r="Q195" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>42430</v>
       </c>
@@ -24253,7 +22051,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>42461</v>
       </c>
@@ -24300,7 +22098,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>42491</v>
       </c>
@@ -24347,7 +22145,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>42522</v>
       </c>
@@ -24394,7 +22192,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>42552</v>
       </c>
@@ -24438,10 +22236,10 @@
         <v>91.76</v>
       </c>
       <c r="Q200" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>42583</v>
       </c>
@@ -24488,7 +22286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>42614</v>
       </c>
@@ -24535,7 +22333,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>42644</v>
       </c>
@@ -24582,7 +22380,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>42675</v>
       </c>
@@ -24629,7 +22427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>42705</v>
       </c>
@@ -24676,7 +22474,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>42736</v>
       </c>
@@ -24720,10 +22518,10 @@
         <v>103.76</v>
       </c>
       <c r="Q206" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>42767</v>
       </c>
@@ -24770,7 +22568,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>42795</v>
       </c>
@@ -24814,10 +22612,10 @@
         <v>97.59</v>
       </c>
       <c r="Q208" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>42826</v>
       </c>
@@ -24864,7 +22662,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>42856</v>
       </c>
@@ -24908,10 +22706,10 @@
         <v>96.97</v>
       </c>
       <c r="Q210" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>42887</v>
       </c>
@@ -24955,10 +22753,10 @@
         <v>96.1</v>
       </c>
       <c r="Q211" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>42917</v>
       </c>
@@ -25002,10 +22800,10 @@
         <v>95.56</v>
       </c>
       <c r="Q212" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>42948</v>
       </c>
@@ -25052,7 +22850,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>42979</v>
       </c>
@@ -25099,7 +22897,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>43009</v>
       </c>
@@ -25146,7 +22944,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>43040</v>
       </c>
@@ -25193,7 +22991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>43070</v>
       </c>
@@ -25240,7 +23038,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>43101</v>
       </c>
@@ -25284,10 +23082,10 @@
         <v>102.04</v>
       </c>
       <c r="Q218" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>43132</v>
       </c>
@@ -25334,7 +23132,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>43160</v>
       </c>
@@ -25378,10 +23176,10 @@
         <v>98.9</v>
       </c>
       <c r="Q220" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>43191</v>
       </c>
@@ -25425,10 +23223,10 @@
         <v>100.35</v>
       </c>
       <c r="Q221" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>43221</v>
       </c>
@@ -25472,10 +23270,10 @@
         <v>104.56</v>
       </c>
       <c r="Q222" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>43252</v>
       </c>
@@ -25522,7 +23320,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>43282</v>
       </c>
@@ -25566,10 +23364,10 @@
         <v>106.29</v>
       </c>
       <c r="Q224" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>43313</v>
       </c>
@@ -25616,7 +23414,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>43344</v>
       </c>
@@ -25663,7 +23461,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>43374</v>
       </c>
@@ -25710,7 +23508,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>43405</v>
       </c>
@@ -25757,7 +23555,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>43435</v>
       </c>
@@ -25804,7 +23602,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>43466</v>
       </c>
@@ -25848,10 +23646,10 @@
         <v>103.54</v>
       </c>
       <c r="Q230" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>43497</v>
       </c>
@@ -25898,7 +23696,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>43525</v>
       </c>
@@ -25945,7 +23743,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>43556</v>
       </c>
@@ -25992,7 +23790,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>43586</v>
       </c>
@@ -26039,7 +23837,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>43617</v>
       </c>
@@ -26083,10 +23881,10 @@
         <v>102.91</v>
       </c>
       <c r="Q235" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>43647</v>
       </c>
@@ -26133,7 +23931,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>43678</v>
       </c>
@@ -26180,7 +23978,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>43709</v>
       </c>
@@ -26224,10 +24022,10 @@
         <v>102.03</v>
       </c>
       <c r="Q238" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>43739</v>
       </c>
@@ -26274,7 +24072,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>43770</v>
       </c>
@@ -26321,7 +24119,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>43800</v>
       </c>
@@ -26365,10 +24163,10 @@
         <v>101.71</v>
       </c>
       <c r="Q241" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>43831</v>
       </c>
@@ -26415,7 +24213,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>43862</v>
       </c>
@@ -26462,7 +24260,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>43891</v>
       </c>
@@ -26509,7 +24307,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>43922</v>
       </c>
@@ -26556,7 +24354,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>43952</v>
       </c>
@@ -26603,7 +24401,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>43983</v>
       </c>
@@ -26647,10 +24445,10 @@
         <v>90.61</v>
       </c>
       <c r="Q247" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>44013</v>
       </c>
@@ -26697,7 +24495,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>44044</v>
       </c>
@@ -26741,10 +24539,10 @@
         <v>92.94</v>
       </c>
       <c r="Q249" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>44075</v>
       </c>
@@ -26788,10 +24586,10 @@
         <v>93.27</v>
       </c>
       <c r="Q250" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>44105</v>
       </c>
@@ -26838,7 +24636,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>44136</v>
       </c>
@@ -26885,7 +24683,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>44166</v>
       </c>
@@ -26929,10 +24727,10 @@
         <v>95.32</v>
       </c>
       <c r="Q253" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>44197</v>
       </c>
@@ -26979,7 +24777,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>44228</v>
       </c>
@@ -27026,7 +24824,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>44256</v>
       </c>
@@ -27073,7 +24871,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>44287</v>
       </c>
@@ -27120,7 +24918,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>44317</v>
       </c>
@@ -27167,7 +24965,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>44348</v>
       </c>
@@ -27211,10 +25009,10 @@
         <v>111.84</v>
       </c>
       <c r="Q259" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>44378</v>
       </c>
@@ -27258,10 +25056,10 @@
         <v>111.77</v>
       </c>
       <c r="Q260" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>44409</v>
       </c>
@@ -27308,7 +25106,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>44440</v>
       </c>
@@ -27355,7 +25153,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>44470</v>
       </c>
@@ -27402,7 +25200,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>44501</v>
       </c>
@@ -27449,7 +25247,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>44531</v>
       </c>
@@ -27493,10 +25291,10 @@
         <v>133.19</v>
       </c>
       <c r="Q265" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>44562</v>
       </c>
@@ -27543,7 +25341,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>44593</v>
       </c>
@@ -27590,7 +25388,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>44621</v>
       </c>
@@ -27634,10 +25432,10 @@
         <v>164.08</v>
       </c>
       <c r="Q268" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="269" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>44652</v>
       </c>
@@ -27684,7 +25482,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>44682</v>
       </c>
@@ -27728,10 +25526,10 @@
         <v>144.57</v>
       </c>
       <c r="Q270" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="271" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>44713</v>
       </c>
@@ -27775,10 +25573,10 @@
         <v>157.11000000000001</v>
       </c>
       <c r="Q271" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>44743</v>
       </c>
@@ -27822,10 +25620,10 @@
         <v>157.51</v>
       </c>
       <c r="Q272" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="273" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>44774</v>
       </c>
@@ -27872,7 +25670,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>44805</v>
       </c>
@@ -27919,7 +25717,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>44835</v>
       </c>
@@ -27966,7 +25764,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>44866</v>
       </c>
@@ -28010,10 +25808,10 @@
         <v>131.18</v>
       </c>
       <c r="Q276" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>44896</v>
       </c>
@@ -28060,7 +25858,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>44927</v>
       </c>
@@ -28107,7 +25905,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>44958</v>
       </c>
@@ -28154,7 +25952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>44986</v>
       </c>
@@ -28201,7 +25999,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>45017</v>
       </c>
@@ -28248,7 +26046,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>45047</v>
       </c>
@@ -28292,10 +26090,10 @@
         <v>116.35</v>
       </c>
       <c r="Q282" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>45078</v>
       </c>
@@ -28342,7 +26140,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>45108</v>
       </c>
@@ -28389,7 +26187,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>45139</v>
       </c>
@@ -28436,7 +26234,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>45170</v>
       </c>
@@ -28483,7 +26281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>45200</v>
       </c>
@@ -28527,10 +26325,10 @@
         <v>123.62</v>
       </c>
       <c r="Q287" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="288" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>45231</v>
       </c>
@@ -28574,10 +26372,10 @@
         <v>118.34</v>
       </c>
       <c r="Q288" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="289" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>45261</v>
       </c>
@@ -28624,7 +26422,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>45292</v>
       </c>
@@ -28671,7 +26469,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>45323</v>
       </c>
@@ -28718,7 +26516,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>45352</v>
       </c>
@@ -28762,10 +26560,10 @@
         <v>124.25</v>
       </c>
       <c r="Q292" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="293" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>45383</v>
       </c>
@@ -28812,7 +26610,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>45413</v>
       </c>
@@ -28856,10 +26654,10 @@
         <v>125.52</v>
       </c>
       <c r="Q294" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="295" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>45444</v>
       </c>
@@ -28906,7 +26704,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>45474</v>
       </c>
@@ -28953,7 +26751,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>45505</v>
       </c>
@@ -29000,7 +26798,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>45536</v>
       </c>
@@ -29044,10 +26842,10 @@
         <v>117.9</v>
       </c>
       <c r="Q298" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="299" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>45566</v>
       </c>
@@ -29094,7 +26892,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>45597</v>
       </c>
@@ -29138,10 +26936,10 @@
         <v>121.4</v>
       </c>
       <c r="Q300" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="301" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>45627</v>
       </c>
@@ -29188,7 +26986,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>45658</v>
       </c>
@@ -29235,7 +27033,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>45689</v>
       </c>
@@ -29282,7 +27080,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>45717</v>
       </c>
@@ -29329,7 +27127,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>45748</v>
       </c>
@@ -29373,10 +27171,10 @@
         <v>122.9</v>
       </c>
       <c r="Q305" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="306" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>45778</v>
       </c>
@@ -29423,7 +27221,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>45809</v>
       </c>
@@ -29470,7 +27268,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>45839</v>
       </c>
@@ -29514,10 +27312,10 @@
         <v>126.21</v>
       </c>
       <c r="Q308" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="309" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>45870</v>
       </c>
@@ -29564,7 +27362,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>45901</v>
       </c>
@@ -29608,10 +27406,10 @@
         <v>125.26</v>
       </c>
       <c r="Q310" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="311" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>45931</v>
       </c>
@@ -29658,7 +27456,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>45962</v>
       </c>
@@ -29705,7 +27503,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>45992</v>
       </c>
@@ -29752,7 +27550,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G314" s="6" t="e">
         <v>#N/A</v>
       </c>
